--- a/docs/progress/GANTT.xlsx
+++ b/docs/progress/GANTT.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Remaining" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Changes!$A$1:$F$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Changes!$A$1:$F$182</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Daily!$A$1:$I$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Progress!$A$1:$Q$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Remaining!$A$1:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Remaining!$A$1:$L$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Gantt!$3:$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,9 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2575" uniqueCount="1073">
-  <si>
-    <t>Gantt, Oct 1 to Dec 12, 2026: generated by tools/make_gantt.py on 2026-10-30 from cb11212; today = 2026-10-30 (red column)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2572" uniqueCount="1084">
+  <si>
+    <t>Gantt, Oct 1 to Dec 12, 2026: generated by tools/make_gantt.py on 2026-10-30 from 181dd9d; today = 2026-10-30 (red column)</t>
   </si>
   <si>
     <t>Legend:</t>
@@ -447,7 +447,7 @@
     <t>Training settings</t>
   </si>
   <si>
-    <t>Repo: history rewrite, merge (1 of 2 done)</t>
+    <t>Repo: history rewrite, merge (2 of 2 done)</t>
   </si>
   <si>
     <t>A6</t>
@@ -465,162 +465,159 @@
     <t>Merge trackA-nosol into local main (shared code, docs, no produced data); tests; push commands for Ritik</t>
   </si>
   <si>
+    <t>2026-10-30</t>
+  </si>
+  <si>
+    <t>Evaluation and Gate 3 (3 of 7 done)</t>
+  </si>
+  <si>
+    <t>A14</t>
+  </si>
+  <si>
+    <t>Gate 3 job plan: every job in order, 2 at a time, limits, dates</t>
+  </si>
+  <si>
+    <t>Evaluate base, prompt-only and the trained versions on Sol (batch 3)</t>
+  </si>
+  <si>
+    <t>start: TODO From; end: before A18 (it waits on it) (inferred)</t>
+  </si>
+  <si>
+    <t>A17</t>
+  </si>
+  <si>
+    <t>Step 13 analysis: 4 measures, hiding check, false-disclosure check, measure 4 on hand-label categories, "tags help more on the inserted tool turn than the past…</t>
+  </si>
+  <si>
+    <t>2026-11-10</t>
+  </si>
+  <si>
+    <t>start: PLAN timeline; end: PLAN timeline (Nov 10–Nov 20): Step 13 analysis</t>
+  </si>
+  <si>
+    <t>A16, L4</t>
+  </si>
+  <si>
+    <t>A18</t>
+  </si>
+  <si>
+    <t>Look-inside rerun on the best version (L1): Step 10 drops at 15/19/23; heads L19H31, L23H17, L15H31: drop, or stay while the answer stops following</t>
+  </si>
+  <si>
+    <t>2026-11-04</t>
+  </si>
+  <si>
+    <t>start: PLAN timeline; end: PLAN timeline (Nov 4–Nov 9): look inside the best version (L1)</t>
+  </si>
+  <si>
+    <t>A21</t>
+  </si>
+  <si>
+    <t>Hand the best version to Tracks B and C (week 15)</t>
+  </si>
+  <si>
+    <t>2026-11-23</t>
+  </si>
+  <si>
+    <t>2026-11-29</t>
+  </si>
+  <si>
+    <t>start: PLAN timeline; end: PLAN timeline (Nov 23–Nov 29): Hand the best version to B and C</t>
+  </si>
+  <si>
+    <t>A33</t>
+  </si>
+  <si>
+    <t>Hugging Face generation for batch 3 (Ritik, Oct 29: all systems and B1 on the training environment's stack; vLLM optional): finetune/hf_engine.py (continuous b…</t>
+  </si>
+  <si>
+    <t>A36</t>
+  </si>
+  <si>
+    <t>Gate 3 in one command (Ritik, Oct 29): finetune/gate3.py --out results/trackA/gpu/eval runs eval.py's report, then writes the verdict per trained version (the…</t>
+  </si>
+  <si>
+    <t>S7: validation loss (1 of 1 done)</t>
+  </si>
+  <si>
+    <t>A28</t>
+  </si>
+  <si>
+    <t>Training needs a baseline (Ritik, Oct 28): the validation loss of base and both epochs of every version (lora, tags, lora_tags, lora_attn3; all four decided Oc…</t>
+  </si>
+  <si>
+    <t>Set A (2 of 2 done)</t>
+  </si>
+  <si>
+    <t>A29</t>
+  </si>
+  <si>
+    <t>Set A, an independent localization set (Ritik, Oct 29): Olmo 3 7B Think on the 34 validation questions (pasted and declared inserted tool turn, 3 runs each; St…</t>
+  </si>
+  <si>
+    <t>A32</t>
+  </si>
+  <si>
+    <t>Rank heads on set A (Step 9 rerun) for B1's head-subset variant; never on the evaluation questions</t>
+  </si>
+  <si>
+    <t>B1: provenance scaling (0 of 1 done)</t>
+  </si>
+  <si>
+    <t>A30</t>
+  </si>
+  <si>
+    <t>B1, provenance-scaled attention at inference (finetune/provenance.py): the forced-answer job on set A's cuts (chooses alpha on set A), then generation on the 3…</t>
+  </si>
+  <si>
+    <t>B2: provenance bias (0 of 1 done)</t>
+  </si>
+  <si>
+    <t>A31</t>
+  </si>
+  <si>
+    <t>B2, provenance-gated attention bias (versions gate3, lora_attn3_gate in train.py): a learned per-head bias on tool-tagged keys in 15/19/23, zero-initialized; L…</t>
+  </si>
+  <si>
+    <t>batch 3's order</t>
+  </si>
+  <si>
+    <t>Thread 1 on Qwen3-8B (0 of 1 done)</t>
+  </si>
+  <si>
+    <t>A37</t>
+  </si>
+  <si>
+    <t>Thread 1 on a second model (Ritik, Oct 30): Qwen3-8B thinking on, Step 3 and Step 10 on Track B's runs; localize on the 24 pilot puzzles (tool_real), replicate…</t>
+  </si>
+  <si>
+    <t>the push; the 10 jobs</t>
+  </si>
+  <si>
+    <t>Track B: test widely</t>
+  </si>
+  <si>
+    <t>Closed models, GPQA (0 of 4 done)</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>Closed-provider keys: a real OpenAI key (the current one is the Voyager key), Anthropic, xAI</t>
+  </si>
+  <si>
+    <t>Arsha (from Nov 3)</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
     <t>not in the repo</t>
   </si>
   <si>
     <t>start: TODO From; end: not in the repo</t>
   </si>
   <si>
-    <t>the plan for main, then Ritik pushes</t>
-  </si>
-  <si>
-    <t>Evaluation and Gate 3 (3 of 7 done)</t>
-  </si>
-  <si>
-    <t>A14</t>
-  </si>
-  <si>
-    <t>Gate 3 job plan: every job in order, 2 at a time, limits, dates</t>
-  </si>
-  <si>
-    <t>Evaluate base, prompt-only and the trained versions on Sol (batch 3)</t>
-  </si>
-  <si>
-    <t>start: TODO From; end: before A18 (it waits on it) (inferred)</t>
-  </si>
-  <si>
-    <t>A17</t>
-  </si>
-  <si>
-    <t>Step 13 analysis: 4 measures, hiding check, false-disclosure check, measure 4 on hand-label categories, "tags help more on the inserted tool turn than the past…</t>
-  </si>
-  <si>
-    <t>2026-11-10</t>
-  </si>
-  <si>
-    <t>start: PLAN timeline; end: PLAN timeline (Nov 10–Nov 20): Step 13 analysis</t>
-  </si>
-  <si>
-    <t>A16, L4</t>
-  </si>
-  <si>
-    <t>A18</t>
-  </si>
-  <si>
-    <t>Look-inside rerun on the best version (L1): Step 10 drops at 15/19/23; heads L19H31, L23H17, L15H31: drop, or stay while the answer stops following</t>
-  </si>
-  <si>
-    <t>2026-11-04</t>
-  </si>
-  <si>
-    <t>start: PLAN timeline; end: PLAN timeline (Nov 4–Nov 9): look inside the best version (L1)</t>
-  </si>
-  <si>
-    <t>A21</t>
-  </si>
-  <si>
-    <t>Hand the best version to Tracks B and C (week 15)</t>
-  </si>
-  <si>
-    <t>2026-11-23</t>
-  </si>
-  <si>
-    <t>2026-11-29</t>
-  </si>
-  <si>
-    <t>start: PLAN timeline; end: PLAN timeline (Nov 23–Nov 29): Hand the best version to B and C</t>
-  </si>
-  <si>
-    <t>A33</t>
-  </si>
-  <si>
-    <t>Hugging Face generation for batch 3 (Ritik, Oct 29: all systems and B1 on the training environment's stack; vLLM optional): finetune/hf_engine.py (continuous b…</t>
-  </si>
-  <si>
-    <t>A36</t>
-  </si>
-  <si>
-    <t>Gate 3 in one command (Ritik, Oct 29): finetune/gate3.py --out results/trackA/gpu/eval runs eval.py's report, then writes the verdict per trained version (the…</t>
-  </si>
-  <si>
-    <t>2026-10-30</t>
-  </si>
-  <si>
-    <t>S7: validation loss (1 of 1 done)</t>
-  </si>
-  <si>
-    <t>A28</t>
-  </si>
-  <si>
-    <t>Training needs a baseline (Ritik, Oct 28): the validation loss of base and both epochs of every version (lora, tags, lora_tags, lora_attn3; all four decided Oc…</t>
-  </si>
-  <si>
-    <t>Set A (2 of 2 done)</t>
-  </si>
-  <si>
-    <t>A29</t>
-  </si>
-  <si>
-    <t>Set A, an independent localization set (Ritik, Oct 29): Olmo 3 7B Think on the 34 validation questions (pasted and declared inserted tool turn, 3 runs each; St…</t>
-  </si>
-  <si>
-    <t>A32</t>
-  </si>
-  <si>
-    <t>Rank heads on set A (Step 9 rerun) for B1's head-subset variant; never on the evaluation questions</t>
-  </si>
-  <si>
-    <t>B1: provenance scaling (0 of 1 done)</t>
-  </si>
-  <si>
-    <t>A30</t>
-  </si>
-  <si>
-    <t>B1, provenance-scaled attention at inference (finetune/provenance.py): the forced-answer job on set A's cuts (chooses alpha on set A), then generation on the 3…</t>
-  </si>
-  <si>
-    <t>B2: provenance bias (0 of 1 done)</t>
-  </si>
-  <si>
-    <t>A31</t>
-  </si>
-  <si>
-    <t>B2, provenance-gated attention bias (versions gate3, lora_attn3_gate in train.py): a learned per-head bias on tool-tagged keys in 15/19/23, zero-initialized; L…</t>
-  </si>
-  <si>
-    <t>batch 3's order</t>
-  </si>
-  <si>
-    <t>Thread 1 on Qwen3-8B (0 of 1 done)</t>
-  </si>
-  <si>
-    <t>A37</t>
-  </si>
-  <si>
-    <t>Thread 1 on a second model (Ritik, Oct 30): Qwen3-8B thinking on, Step 3 and Step 10 on Track B's runs; localize on the 24 pilot puzzles (tool_real), replicate…</t>
-  </si>
-  <si>
-    <t>the push; the 10 jobs</t>
-  </si>
-  <si>
-    <t>Track B: test widely</t>
-  </si>
-  <si>
-    <t>Closed models, GPQA (0 of 4 done)</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>Closed-provider keys: a real OpenAI key (the current one is the Voyager key), Anthropic, xAI</t>
-  </si>
-  <si>
-    <t>Arsha (from Nov 3)</t>
-  </si>
-  <si>
-    <t>2026-10-05</t>
-  </si>
-  <si>
     <t>keys</t>
   </si>
   <si>
@@ -972,7 +969,7 @@
     <t>Repo, docs and handoff</t>
   </si>
   <si>
-    <t>Handoffs, repo, docs (3 of 6 done)</t>
+    <t>Handoffs, repo, docs (4 of 6 done)</t>
   </si>
   <si>
     <t>H1</t>
@@ -1446,7 +1443,7 @@
     <t>F26, F27, F28, F32</t>
   </si>
   <si>
-    <t>8380e56 f369bf6 88415d6 e4e1b1f 65189dc faddef2 df5377d af2f2fb 42a96ab fd1a679 1339638</t>
+    <t>8380e56 f369bf6 88415d6 e4e1b1f 65189dc faddef2 df5377d af2f2fb 42a96ab fd1a679 1339638 1b52c43 181dd9d</t>
   </si>
   <si>
     <t>2026-10-30_0900_A_setA-step10-replicates.md, 2026-10-30_0905_A_b1-alpha-chosen.md, 2026-10-30_0910_A_gate3-interim.md, 2026-10-30_1010_A_setA-step9-prereg.md, 2026-10-30_1035_A_setA-step9-replicates.md, 2026-10-30_1045_A_l4-label-sheets.md, 2026-10-30_1145_A_qwen8b-mech-prereg.md, 2026-10-30_1715_A_b1-generation-rule.md</t>
@@ -1461,13 +1458,13 @@
     <t>F25, F29</t>
   </si>
   <si>
-    <t>60979c4 8380e56 f369bf6 6b2ad02 88415d6</t>
+    <t>60979c4 8380e56 f369bf6 6b2ad02 88415d6 1b52c43</t>
   </si>
   <si>
     <t>2026-10-30_0400_B_b15-results.md, 2026-10-30_0915_B_qwen3-8b-thinking-on-off.md</t>
   </si>
   <si>
-    <t>01:10 C15 done (200 + 100 cases, 0 errors; F24): F18 replicates on 100 fresh items (Olmo −55 [−70, −38], defers; Qwen3 −6 [−15, +4]); redaction restores part of Olmo's check again (+25 [+11, +38]), on MMLU-Pro and puzzles; H23 not supported (+14 [−13, +37]); C14's cheaper rule fails (c1, c2 not confirmed), shipping 4 and 7 wrong of 53 where the checker ships none; F15's bare letter holds || 08:50 C16 pre-registered (Ritik approved Oct 30): C15's 100 fresh items, the solver told B15's instruction (--disclose); plus_explanation reviews (the final answer; answer_only shows only the letter, a ruling) against a same-day control on C15's solver and C15's answer_only; two-sided, C11's 20-point margin; dry runs ~700 calls || 09:20 C13 (F30): Granite 4.1 30B −5 [−26, +15], Mistral Small 3.2 24B +19 [+10, +30]: neither defers; over six reviewers and four families only Olmo's two do ("Olmo-specific", as pre-registered) || 10:25 C17 pre-registered (Ritik approved): C15's saved final answers with one fixed sentence appended, names the lookup tool vs own step-by-step working (same length), against C16's unchanged control; Olmo 3.1 32B and Qwen3 30B Instruct, plus_explanation; main (b) names − own, (a) names − unchanged, two-sided with C11's margin; 400 reviews || 10:30 C16 (F31): the solver named the tool after 34 of 55 bad lookups (C15: 5) and still took the wrong letter (54 of 55); the Olmo reviewer seeing that answer corrects 25 against 36 of 53 (−21 [−34, −8]: unclear by the 20-point rule), Qwen3 44 against 44 (no change); descriptive: Olmo −41 where the tool was named, +10 where not. Also at 10:00: F28 corrected (the guide note isn't what the targets were made with), Gate 3's three-part framing and cautionary claim, L4 labels first, the title-question reading (F29), CLAIMS 2.1 family-specific || 11:00 C17 (F33): a fixed sentence naming the lookup tool, added to C15's bare answers, doesn't move the Olmo reviewer (names − own working 37 vs 37 of 53, +0 [−11, +11]; names − unchanged +2); Qwen3 no change; C16's drop went with the solver's own explanations (median 353 chars vs 11), not the mention (H33, untested) || 17:00 C18 pre-registered (Ritik approved): H33, is the cue the argument? C16's 34 named bad-lookup answers, unchanged vs the tool sentences removed (median 474 → 126 chars), Olmo 3.1 32B and Qwen3 30B Instruct, plus_explanation; main stripped − unchanged, two-sided, C11's margin; C17's own-working version as the length reference; 136 reviews || 17:20 C18 (F34): removing C16's sentences that cite the tool restores the Olmo reviewer's check: 25 vs 9 of 34, +47 [+29, +65] (more corrections: "the tool mentions are part of the cue"; H33 not supported); Qwen3 no change; re-review identical to C16; with C17: the cue is the solver's citation of the tool's letter as authority, not a generic label nor the remaining working (H34)</t>
+    <t>01:10 C15 done (200 + 100 cases, 0 errors; F24): F18 replicates on 100 fresh items (Olmo −55 [−70, −38], defers; Qwen3 −6 [−15, +4]); redaction restores part of Olmo's check again (+25 [+11, +38]), on MMLU-Pro and puzzles; H23 not supported (+14 [−13, +37]); C14's cheaper rule fails (c1, c2 not confirmed), shipping 4 and 7 wrong of 53 where the checker ships none; F15's bare letter holds || 08:50 C16 pre-registered (Ritik approved Oct 30): C15's 100 fresh items, the solver told B15's instruction (--disclose); plus_explanation reviews (the final answer; answer_only shows only the letter, a ruling) against a same-day control on C15's solver and C15's answer_only; two-sided, C11's 20-point margin; dry runs ~700 calls || 09:20 C13 (F30): Granite 4.1 30B −5 [−26, +15], Mistral Small 3.2 24B +19 [+10, +30]: neither defers; over six reviewers and four families only Olmo's two do ("Olmo-specific", as pre-registered) || 10:25 C17 pre-registered (Ritik approved): C15's saved final answers with one fixed sentence appended, names the lookup tool vs own step-by-step working (same length), against C16's unchanged control; Olmo 3.1 32B and Qwen3 30B Instruct, plus_explanation; main (b) names − own, (a) names − unchanged, two-sided with C11's margin; 400 reviews || 10:30 C16 (F31): the solver named the tool after 34 of 55 bad lookups (C15: 5) and still took the wrong letter (54 of 55); the Olmo reviewer seeing that answer corrects 25 against 36 of 53 (−21 [−34, −8]: unclear by the 20-point rule), Qwen3 44 against 44 (no change); descriptive: Olmo −41 where the tool was named, +10 where not. Also at 10:00: F28 corrected (the guide note isn't what the targets were made with), Gate 3's three-part framing and cautionary claim, L4 labels first, the title-question reading (F29), CLAIMS 2.1 family-specific || 11:00 C17 (F33): a fixed sentence naming the lookup tool, added to C15's bare answers, doesn't move the Olmo reviewer (names − own working 37 vs 37 of 53, +0 [−11, +11]; names − unchanged +2); Qwen3 no change; C16's drop went with the solver's own explanations (median 353 chars vs 11), not the mention (H33, untested) || 17:00 C18 pre-registered (Ritik approved): H33, is the cue the argument? C16's 34 named bad-lookup answers, unchanged vs the tool sentences removed (median 474 → 126 chars), Olmo 3.1 32B and Qwen3 30B Instruct, plus_explanation; main stripped − unchanged, two-sided, C11's margin; C17's own-working version as the length reference; 136 reviews || 17:20 C18 (F34): removing C16's sentences that cite the tool restores the Olmo reviewer's check: 25 vs 9 of 34, +47 [+29, +65] (more corrections: "the tool mentions are part of the cue"; H33 not supported); Qwen3 no change; re-review identical to C16; with C17: the cue is the solver's citation of the tool's letter as authority, not a generic label nor the remaining working (H34) || 18:05 Track C handed to Shrey: TRACK_C.md final, his plan C19–C24, a portable Sol kit and SOL_SETUP.md, his own Voyager key; th…</t>
   </si>
   <si>
     <t>200 + 100 cases; 700 calls; 400 reviews; 136 reviews</t>
@@ -1476,10 +1473,10 @@
     <t>F24, F30, F31, F33, F34</t>
   </si>
   <si>
-    <t>8dff157 8380e56 f369bf6 6b2ad02 88415d6 16ef2dc 65189dc e2576ff 4bdfe78 1928820 1339638 cb11212</t>
-  </si>
-  <si>
-    <t>2026-10-30_0110_C_c15-results.md, 2026-10-30_0850_C_c16-prereg.md, 2026-10-30_0920_C_c13-granite-mistral.md, 2026-10-30_1025_C_c17-prereg.md, 2026-10-30_1030_C_c16-results.md, 2026-10-30_1100_C_c17-results.md, 2026-10-30_1700_C_c18-prereg.md, 2026-10-30_1720_C_c18-results.md</t>
+    <t>8dff157 8380e56 f369bf6 6b2ad02 88415d6 16ef2dc 65189dc e2576ff 4bdfe78 1928820 1339638 cb11212 1b52c43 181dd9d</t>
+  </si>
+  <si>
+    <t>2026-10-30_0110_C_c15-results.md, 2026-10-30_0850_C_c16-prereg.md, 2026-10-30_0920_C_c13-granite-mistral.md, 2026-10-30_1025_C_c17-prereg.md, 2026-10-30_1030_C_c16-results.md, 2026-10-30_1100_C_c17-results.md, 2026-10-30_1700_C_c18-prereg.md, 2026-10-30_1720_C_c18-results.md, 2026-10-30_1805_C_handoff-to-shrey.md</t>
   </si>
   <si>
     <t>From commits (no session log for this track that day): Gate 3 corrected, the label order, and set A's Step 9 pre-registered before it is read (Oct 30, 10:… | C16 read by its pre-registered rule; the title question; C13's claim (Oct 30, 10:30; FINDINGS F31).… | Daily Oct 30, late morning (10:40): Sol's night read (F26-F30, F28 corrected), C16 run and read (F3… | L4, Gate 3's blind label sheets (Oct 30, 10:45; Ritik's rules). eval.py --label-sheets: part 1 = Lo… | C18 read (FINDINGS F34), B1 generation's rule and L4's order fixed before results (Oct 30, 17:15-17…</t>
@@ -1488,51 +1485,96 @@
     <t>e4e1b1f 16ef2dc 65189dc df5377d 1339638</t>
   </si>
   <si>
-    <t>08:45 Sol's night: every job exit 0 (prompt_only, lora, set A Steps 9/10, B1 forced, Qwen3-8B, C13; C13 had its inputs); the QoS re-checked (2 running, 10 submitted, 960 GPU-min: README right); command 4 adjusted (all 10 now, Ritik's order, alpha applied); the push (427f39e..f369bf6); Ritik's decisions (rater asks, C16, B15 wording, the story headline); set A's distance split fixed || Daily: The night of Oct 29–30 (no Sol): C14, C15 (F24), B15 (F25) and their numbers; Gate 3 in one command, B2's bias log, the rater guide, the handoffs and bundles; a review of the night's code (two fixes, readings unchanged); six decisions waiting; the morning Sol lines (queue, copy-backs for set A, batch 3, Qwen3-8B and C13, B1's alpha, then the 10 submissions in Ritik's order)</t>
+    <t>08:45 Sol's night: every job exit 0 (prompt_only, lora, set A Steps 9/10, B1 forced, Qwen3-8B, C13; C13 had its inputs); the QoS re-checked (2 running, 10 submitted, 960 GPU-min: README right); command 4 adjusted (all 10 now, Ritik's order, alpha applied); the push (427f39e..f369bf6); Ritik's decisions (rater asks, C16, B15 wording, the story headline); set A's distance split fixed || 17:25 The Gantt sheet (tools/make_gantt.py → docs/progress/GANTT.xlsx, gantt.png, STATUS.md), generated from git, the logs, TODO, PLAN and FINDINGS; 59 of 86 tasks done (A 27/37, B 10/15, C 17/23, labels 2/5, repo 3/6), ~172 h left; milestones; 36 inferred dates || 17:40 Repository cleanup: inventory of 521 tracked files by reference scan (134 with no textual reference: tests, files loaded by name, the progress deck's assets, figures, summaries; none stale or irrelevant), so none removed; the Oct 4 bundle to the gitignored results/archive/, an untracked note and 16 .DS_Store files to ~/cse598_trash_20261030/; tools/check_links.py: 0 broken links, 0 missing RUNBOOK scripts || 18:00 The supplement (tools/make_supplement.py → docs/paper/supplement/, 46 files): EVIDENCE (34 F entries, 129 CLAIMS numbers checked), PREREGISTRATIONS (23 rules, after-the-fact readings flagged), DEVIATIONS, TRAPS, tables, figures, APPENDIX_OUTLINE; what it caught and was fixed (CLAIMS numbers, F32's rounding), log names set ahead of commits, same-minute starts || Daily: The night of Oct 29–30 (no Sol): C14, C15 (F24), B15 (F25) and their numbers; Gate 3 in one command, B2's bias log, the rater guide, the handoffs and bundles; a review of the night's code (two fixes, readings unchanged); six decisions waiting; the morning Sol lines (queue, copy-backs for set A, batch 3, Qwen3-8B and C13, B1's alpha, then the 10 submissions in Ritik's order)</t>
   </si>
   <si>
     <t>960 GPU-min; compute (daily): Sol: nothing submitted or changed (Sol was full). The queue as last seen at 21:56 is in command 0 below.; Voyager, under the power guard, 4 in flight, 0 errors: C15: 22:48 – 00:45 (200 solver-and-checker cases, then 600 reviews). B15: 23:57 – 03:44 (1,620 runs). The Mac was on battery from about 23:50 (97% → 57% at 03:44). The guard never paused. It ended at 03:45 with every job done; nothing has run on Voyager since. The battery is at 39% at 06:55: worth plugging in before the next Voyager run.</t>
   </si>
   <si>
+    <t>c0f8141 bbc944d 4fa9c0c</t>
+  </si>
+  <si>
+    <t>2026-10-30_0845_ALL_sol-morning-and-decisions.md, 2026-10-30_1725_ALL_gantt.md, 2026-10-30_1740_ALL_cleanup.md, 2026-10-30_1800_ALL_supplement.md, DAILY_2026-10-30.md</t>
+  </si>
+  <si>
+    <t>Time (MST)</t>
+  </si>
+  <si>
+    <t>Hash</t>
+  </si>
+  <si>
+    <t>Track (A, B, C, Labels, Setup, ALL; + = several)</t>
+  </si>
+  <si>
+    <t>Summary (first 120 characters)</t>
+  </si>
+  <si>
+    <t>Files</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>181dd9d</t>
+  </si>
+  <si>
+    <t>A+C</t>
+  </si>
+  <si>
+    <t>The supplement, generated and tested; what it caught, fixed; the cleanup and handoff logs (Oct 30, 17:40-18:05). tools/…</t>
+  </si>
+  <si>
+    <t>17:36</t>
+  </si>
+  <si>
+    <t>4fa9c0c</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>TODO: A7 (main fast-forwarded and pushed) and R1 (GitHub main has had the Oct 21 Voyager IDs since Oct 29) done.</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>1b52c43</t>
+  </si>
+  <si>
+    <t>A+B+C</t>
+  </si>
+  <si>
+    <t>A portable Sol kit, so Shrey runs Track C's GPU jobs under his own account (Oct 30). env.sh derives every path from $US…</t>
+  </si>
+  <si>
+    <t>17:22</t>
+  </si>
+  <si>
+    <t>bbc944d</t>
+  </si>
+  <si>
+    <t>The Gantt sheet, generated from the repo (Oct 30). tools/make_gantt.py reads git log, the session logs and INDEX, the d…</t>
+  </si>
+  <si>
+    <t>16:59</t>
+  </si>
+  <si>
+    <t>cb11212</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Track C handed to Shrey (Oct 30). TRACK_C.md final: the setup; the story in order (F18, F19, F21-F24, F30, F31, F33, F3…</t>
+  </si>
+  <si>
+    <t>16:56</t>
+  </si>
+  <si>
     <t>c0f8141</t>
   </si>
   <si>
-    <t>2026-10-30_0845_ALL_sol-morning-and-decisions.md, DAILY_2026-10-30.md</t>
-  </si>
-  <si>
-    <t>Time (MST)</t>
-  </si>
-  <si>
-    <t>Hash</t>
-  </si>
-  <si>
-    <t>Track (A, B, C, Labels, Setup, ALL; + = several)</t>
-  </si>
-  <si>
-    <t>Summary (first 120 characters)</t>
-  </si>
-  <si>
-    <t>Files</t>
-  </si>
-  <si>
-    <t>16:59</t>
-  </si>
-  <si>
-    <t>cb11212</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Track C handed to Shrey (Oct 30). TRACK_C.md final: the setup; the story in order (F18, F19, F21-F24, F30, F31, F33, F3…</t>
-  </si>
-  <si>
-    <t>16:56</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
     <t>Cleanup tools (Oct 30): tools/check_links.py checks every internal markdown link in the tracked .md files and every scr…</t>
   </si>
   <si>
@@ -1659,9 +1701,6 @@
     <t>88415d6</t>
   </si>
   <si>
-    <t>A+B+C</t>
-  </si>
-  <si>
     <t>Sol's night read by the rules fixed in advance (Oct 30, 08:45-09:20; FINDINGS F26-F30). Every Oct 29 job ended with exi…</t>
   </si>
   <si>
@@ -1755,9 +1794,6 @@
     <t>26b008a</t>
   </si>
   <si>
-    <t>A+C</t>
-  </si>
-  <si>
     <t>C13 coded (no runs): a third and fourth reviewer family on Sol, IBM Granite 4.1 30B (ibm-granite/granite-4.1-30b@4fae62…</t>
   </si>
   <si>
@@ -3123,7 +3159,7 @@
     <t>Read as in progress (no status word in TODO): B9.</t>
   </si>
   <si>
-    <t>Blocked because 'Blocked by' names an outside step (push, rater, keys, decision): A37, L4, R1.</t>
+    <t>Blocked because 'Blocked by' names an outside step (push, rater, keys, decision): A37, L4.</t>
   </si>
   <si>
     <t>Not in TODO yet (from session logs or commits): none.</t>
@@ -3235,9 +3271,6 @@
   </si>
   <si>
     <t>2 min</t>
-  </si>
-  <si>
-    <t>30 min</t>
   </si>
   <si>
     <t>group 1: ~2 h per rater</t>
@@ -3468,10 +3501,10 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5724,7 +5757,7 @@
         <v>145</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D51" s="17" t="s">
         <v>31</v>
@@ -5736,22 +5769,20 @@
         <v>146</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="H51" s="17" t="s">
-        <v>148</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="H51" s="17"/>
       <c r="I51" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="AJ51" s="7"/>
-      <c r="AK51" s="7"/>
-      <c r="AL51" s="7"/>
+      <c r="AJ51" s="4"/>
+      <c r="AK51" s="4"/>
+      <c r="AL51" s="4"/>
       <c r="AM51" s="20"/>
     </row>
     <row r="52" spans="1:69" outlineLevel="1">
       <c r="A52" s="10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
@@ -5765,10 +5796,10 @@
     </row>
     <row r="53" spans="1:69" outlineLevel="2">
       <c r="A53" s="17" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>3</v>
@@ -5798,7 +5829,7 @@
         <v>137</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>4</v>
@@ -5813,7 +5844,7 @@
         <v>135</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H54" s="17"/>
       <c r="I54" s="17" t="s">
@@ -5837,10 +5868,10 @@
     </row>
     <row r="55" spans="1:69" outlineLevel="2">
       <c r="A55" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>5</v>
@@ -5849,16 +5880,16 @@
         <v>31</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>126</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I55" s="17" t="s">
         <v>48</v>
@@ -5878,10 +5909,10 @@
     </row>
     <row r="56" spans="1:69" outlineLevel="2">
       <c r="A56" s="17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>5</v>
@@ -5890,13 +5921,13 @@
         <v>31</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>135</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>137</v>
@@ -5914,10 +5945,10 @@
     </row>
     <row r="57" spans="1:69" outlineLevel="2">
       <c r="A57" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>5</v>
@@ -5926,13 +5957,13 @@
         <v>31</v>
       </c>
       <c r="E57" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="G57" s="17" t="s">
         <v>165</v>
-      </c>
-      <c r="F57" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="G57" s="17" t="s">
-        <v>167</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>137</v>
@@ -5951,10 +5982,10 @@
     </row>
     <row r="58" spans="1:69" outlineLevel="2">
       <c r="A58" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>3</v>
@@ -5980,10 +6011,10 @@
     </row>
     <row r="59" spans="1:69" outlineLevel="2">
       <c r="A59" s="17" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C59" s="17" t="s">
         <v>3</v>
@@ -5995,7 +6026,7 @@
         <v>119</v>
       </c>
       <c r="F59" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G59" s="17" t="s">
         <v>47</v>
@@ -6005,11 +6036,11 @@
         <v>48</v>
       </c>
       <c r="AL59" s="4"/>
-      <c r="AM59" s="21"/>
+      <c r="AM59" s="20"/>
     </row>
     <row r="60" spans="1:69" outlineLevel="1">
       <c r="A60" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
@@ -6023,10 +6054,10 @@
     </row>
     <row r="61" spans="1:69" outlineLevel="2">
       <c r="A61" s="17" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>3</v>
@@ -6054,7 +6085,7 @@
     </row>
     <row r="62" spans="1:69" outlineLevel="1">
       <c r="A62" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
@@ -6068,10 +6099,10 @@
     </row>
     <row r="63" spans="1:69" outlineLevel="2">
       <c r="A63" s="17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C63" s="17" t="s">
         <v>3</v>
@@ -6083,7 +6114,7 @@
         <v>119</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G63" s="17" t="s">
         <v>47</v>
@@ -6093,14 +6124,14 @@
         <v>48</v>
       </c>
       <c r="AL63" s="4"/>
-      <c r="AM63" s="21"/>
+      <c r="AM63" s="20"/>
     </row>
     <row r="64" spans="1:69" outlineLevel="2">
       <c r="A64" s="17" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C64" s="17" t="s">
         <v>3</v>
@@ -6112,23 +6143,23 @@
         <v>119</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G64" s="17" t="s">
         <v>47</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I64" s="17" t="s">
         <v>48</v>
       </c>
       <c r="AL64" s="4"/>
-      <c r="AM64" s="21"/>
+      <c r="AM64" s="20"/>
     </row>
     <row r="65" spans="1:60" outlineLevel="1">
       <c r="A65" s="10" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
@@ -6142,10 +6173,10 @@
     </row>
     <row r="66" spans="1:60" outlineLevel="2">
       <c r="A66" s="17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C66" s="17" t="s">
         <v>4</v>
@@ -6163,7 +6194,7 @@
         <v>127</v>
       </c>
       <c r="H66" s="17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I66" s="17" t="s">
         <v>48</v>
@@ -6194,7 +6225,7 @@
     </row>
     <row r="67" spans="1:60" outlineLevel="1">
       <c r="A67" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
@@ -6208,10 +6239,10 @@
     </row>
     <row r="68" spans="1:60" outlineLevel="2">
       <c r="A68" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C68" s="17" t="s">
         <v>5</v>
@@ -6229,7 +6260,7 @@
         <v>127</v>
       </c>
       <c r="H68" s="17" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I68" s="17" t="s">
         <v>48</v>
@@ -6259,7 +6290,7 @@
     </row>
     <row r="69" spans="1:60" outlineLevel="1">
       <c r="A69" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
@@ -6273,10 +6304,10 @@
     </row>
     <row r="70" spans="1:60" outlineLevel="2">
       <c r="A70" s="17" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C70" s="17" t="s">
         <v>6</v>
@@ -6285,7 +6316,7 @@
         <v>31</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>126</v>
@@ -6294,12 +6325,12 @@
         <v>127</v>
       </c>
       <c r="H70" s="17" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I70" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="AM70" s="20"/>
+      <c r="AM70" s="21"/>
       <c r="AN70" s="6"/>
       <c r="AO70" s="6"/>
       <c r="AP70" s="6"/>
@@ -6324,7 +6355,7 @@
     </row>
     <row r="71" spans="1:60">
       <c r="A71" s="15" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -6338,7 +6369,7 @@
     </row>
     <row r="72" spans="1:60" outlineLevel="1">
       <c r="A72" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
@@ -6352,28 +6383,28 @@
     </row>
     <row r="73" spans="1:60" outlineLevel="2">
       <c r="A73" s="17" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C73" s="17" t="s">
         <v>6</v>
       </c>
       <c r="D73" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="F73" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="G73" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="E73" s="17" t="s">
+      <c r="H73" s="17" t="s">
         <v>197</v>
-      </c>
-      <c r="F73" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="G73" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="H73" s="17" t="s">
-        <v>198</v>
       </c>
       <c r="I73" s="17" t="s">
         <v>48</v>
@@ -6403,32 +6434,32 @@
       <c r="AJ73" s="7"/>
       <c r="AK73" s="7"/>
       <c r="AL73" s="7"/>
-      <c r="AM73" s="20"/>
+      <c r="AM73" s="21"/>
     </row>
     <row r="74" spans="1:60" outlineLevel="2">
       <c r="A74" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="B74" s="17" t="s">
         <v>199</v>
-      </c>
-      <c r="B74" s="17" t="s">
-        <v>200</v>
       </c>
       <c r="C74" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="F74" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I74" s="17" t="s">
         <v>48</v>
@@ -6437,28 +6468,28 @@
     </row>
     <row r="75" spans="1:60" outlineLevel="2">
       <c r="A75" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="B75" s="17" t="s">
         <v>202</v>
-      </c>
-      <c r="B75" s="17" t="s">
-        <v>203</v>
       </c>
       <c r="C75" s="17" t="s">
         <v>6</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E75" s="17" t="s">
         <v>77</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="G75" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="H75" s="17" t="s">
         <v>204</v>
-      </c>
-      <c r="H75" s="17" t="s">
-        <v>205</v>
       </c>
       <c r="I75" s="17" t="s">
         <v>48</v>
@@ -6468,41 +6499,41 @@
       <c r="AJ75" s="7"/>
       <c r="AK75" s="7"/>
       <c r="AL75" s="7"/>
-      <c r="AM75" s="20"/>
+      <c r="AM75" s="21"/>
     </row>
     <row r="76" spans="1:60" outlineLevel="2">
       <c r="A76" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B76" s="17" t="s">
         <v>206</v>
-      </c>
-      <c r="B76" s="17" t="s">
-        <v>207</v>
       </c>
       <c r="C76" s="17" t="s">
         <v>6</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I76" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="AM76" s="20"/>
+      <c r="AM76" s="21"/>
     </row>
     <row r="77" spans="1:60" outlineLevel="1">
       <c r="A77" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
@@ -6516,10 +6547,10 @@
     </row>
     <row r="78" spans="1:60" outlineLevel="2">
       <c r="A78" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B78" s="17" t="s">
         <v>210</v>
-      </c>
-      <c r="B78" s="17" t="s">
-        <v>211</v>
       </c>
       <c r="C78" s="17" t="s">
         <v>3</v>
@@ -6534,7 +6565,7 @@
         <v>67</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H78" s="17"/>
       <c r="I78" s="17" t="s">
@@ -6551,10 +6582,10 @@
     </row>
     <row r="79" spans="1:60" outlineLevel="2">
       <c r="A79" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="B79" s="17" t="s">
         <v>213</v>
-      </c>
-      <c r="B79" s="17" t="s">
-        <v>214</v>
       </c>
       <c r="C79" s="17" t="s">
         <v>3</v>
@@ -6581,10 +6612,10 @@
     </row>
     <row r="80" spans="1:60" outlineLevel="2">
       <c r="A80" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="B80" s="17" t="s">
         <v>215</v>
-      </c>
-      <c r="B80" s="17" t="s">
-        <v>216</v>
       </c>
       <c r="C80" s="17" t="s">
         <v>3</v>
@@ -6602,7 +6633,7 @@
         <v>47</v>
       </c>
       <c r="H80" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I80" s="17" t="s">
         <v>48</v>
@@ -6613,28 +6644,28 @@
     </row>
     <row r="81" spans="1:48" outlineLevel="2">
       <c r="A81" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="B81" s="17" t="s">
         <v>217</v>
-      </c>
-      <c r="B81" s="17" t="s">
-        <v>218</v>
       </c>
       <c r="C81" s="17" t="s">
         <v>4</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E81" s="17" t="s">
         <v>67</v>
       </c>
       <c r="F81" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="G81" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="G81" s="17" t="s">
+      <c r="H81" s="17" t="s">
         <v>220</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>221</v>
       </c>
       <c r="I81" s="17" t="s">
         <v>48</v>
@@ -6655,10 +6686,10 @@
     </row>
     <row r="82" spans="1:48" outlineLevel="2">
       <c r="A82" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="B82" s="17" t="s">
         <v>222</v>
-      </c>
-      <c r="B82" s="17" t="s">
-        <v>223</v>
       </c>
       <c r="C82" s="17" t="s">
         <v>3</v>
@@ -6684,10 +6715,10 @@
     </row>
     <row r="83" spans="1:48" outlineLevel="2">
       <c r="A83" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="B83" s="17" t="s">
         <v>224</v>
-      </c>
-      <c r="B83" s="17" t="s">
-        <v>225</v>
       </c>
       <c r="C83" s="17" t="s">
         <v>3</v>
@@ -6713,10 +6744,10 @@
     </row>
     <row r="84" spans="1:48" outlineLevel="2">
       <c r="A84" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="B84" s="17" t="s">
         <v>226</v>
-      </c>
-      <c r="B84" s="17" t="s">
-        <v>227</v>
       </c>
       <c r="C84" s="17" t="s">
         <v>3</v>
@@ -6731,7 +6762,7 @@
         <v>67</v>
       </c>
       <c r="G84" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H84" s="17"/>
       <c r="I84" s="17" t="s">
@@ -6742,10 +6773,10 @@
     </row>
     <row r="85" spans="1:48" outlineLevel="2">
       <c r="A85" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="B85" s="17" t="s">
         <v>228</v>
-      </c>
-      <c r="B85" s="17" t="s">
-        <v>229</v>
       </c>
       <c r="C85" s="17" t="s">
         <v>3</v>
@@ -6771,10 +6802,10 @@
     </row>
     <row r="86" spans="1:48" outlineLevel="2">
       <c r="A86" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C86" s="17" t="s">
         <v>3</v>
@@ -6792,7 +6823,7 @@
         <v>47</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I86" s="17" t="s">
         <v>48</v>
@@ -6803,10 +6834,10 @@
     </row>
     <row r="87" spans="1:48" outlineLevel="2">
       <c r="A87" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="B87" s="17" t="s">
         <v>232</v>
-      </c>
-      <c r="B87" s="17" t="s">
-        <v>233</v>
       </c>
       <c r="C87" s="17" t="s">
         <v>3</v>
@@ -6818,7 +6849,7 @@
         <v>119</v>
       </c>
       <c r="F87" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G87" s="17" t="s">
         <v>47</v>
@@ -6828,11 +6859,11 @@
         <v>48</v>
       </c>
       <c r="AL87" s="4"/>
-      <c r="AM87" s="21"/>
+      <c r="AM87" s="20"/>
     </row>
     <row r="88" spans="1:48" outlineLevel="1">
       <c r="A88" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
@@ -6846,10 +6877,10 @@
     </row>
     <row r="89" spans="1:48" outlineLevel="2">
       <c r="A89" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="B89" s="17" t="s">
         <v>235</v>
-      </c>
-      <c r="B89" s="17" t="s">
-        <v>236</v>
       </c>
       <c r="C89" s="17" t="s">
         <v>3</v>
@@ -6861,7 +6892,7 @@
         <v>67</v>
       </c>
       <c r="F89" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G89" s="17" t="s">
         <v>47</v>
@@ -6873,11 +6904,11 @@
       <c r="AJ89" s="4"/>
       <c r="AK89" s="4"/>
       <c r="AL89" s="4"/>
-      <c r="AM89" s="21"/>
+      <c r="AM89" s="20"/>
     </row>
     <row r="90" spans="1:48">
       <c r="A90" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
@@ -6891,7 +6922,7 @@
     </row>
     <row r="91" spans="1:48" outlineLevel="1">
       <c r="A91" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
@@ -6905,10 +6936,10 @@
     </row>
     <row r="92" spans="1:48" outlineLevel="2">
       <c r="A92" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="B92" s="17" t="s">
         <v>239</v>
-      </c>
-      <c r="B92" s="17" t="s">
-        <v>240</v>
       </c>
       <c r="C92" s="17" t="s">
         <v>3</v>
@@ -6923,7 +6954,7 @@
         <v>67</v>
       </c>
       <c r="G92" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H92" s="17"/>
       <c r="I92" s="17" t="s">
@@ -6934,10 +6965,10 @@
     </row>
     <row r="93" spans="1:48" outlineLevel="2">
       <c r="A93" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="B93" s="17" t="s">
         <v>242</v>
-      </c>
-      <c r="B93" s="17" t="s">
-        <v>243</v>
       </c>
       <c r="C93" s="17" t="s">
         <v>3</v>
@@ -6964,10 +6995,10 @@
     </row>
     <row r="94" spans="1:48" outlineLevel="2">
       <c r="A94" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="B94" s="17" t="s">
         <v>244</v>
-      </c>
-      <c r="B94" s="17" t="s">
-        <v>245</v>
       </c>
       <c r="C94" s="17" t="s">
         <v>3</v>
@@ -6982,7 +7013,7 @@
         <v>67</v>
       </c>
       <c r="G94" s="17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H94" s="17"/>
       <c r="I94" s="17" t="s">
@@ -6998,10 +7029,10 @@
     </row>
     <row r="95" spans="1:48" outlineLevel="2">
       <c r="A95" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="B95" s="17" t="s">
         <v>247</v>
-      </c>
-      <c r="B95" s="17" t="s">
-        <v>248</v>
       </c>
       <c r="C95" s="17" t="s">
         <v>3</v>
@@ -7016,7 +7047,7 @@
         <v>67</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H95" s="17"/>
       <c r="I95" s="17" t="s">
@@ -7027,7 +7058,7 @@
     </row>
     <row r="96" spans="1:48" outlineLevel="1">
       <c r="A96" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B96" s="10"/>
       <c r="C96" s="10"/>
@@ -7041,10 +7072,10 @@
     </row>
     <row r="97" spans="1:53" outlineLevel="2">
       <c r="A97" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="B97" s="17" t="s">
         <v>250</v>
-      </c>
-      <c r="B97" s="17" t="s">
-        <v>251</v>
       </c>
       <c r="C97" s="17" t="s">
         <v>3</v>
@@ -7059,7 +7090,7 @@
         <v>67</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H97" s="17"/>
       <c r="I97" s="17" t="s">
@@ -7072,10 +7103,10 @@
     </row>
     <row r="98" spans="1:53" outlineLevel="2">
       <c r="A98" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="B98" s="17" t="s">
         <v>253</v>
-      </c>
-      <c r="B98" s="17" t="s">
-        <v>254</v>
       </c>
       <c r="C98" s="17" t="s">
         <v>3</v>
@@ -7093,7 +7124,7 @@
         <v>47</v>
       </c>
       <c r="H98" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I98" s="17" t="s">
         <v>48</v>
@@ -7104,10 +7135,10 @@
     </row>
     <row r="99" spans="1:53" outlineLevel="2">
       <c r="A99" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="B99" s="17" t="s">
         <v>256</v>
-      </c>
-      <c r="B99" s="17" t="s">
-        <v>257</v>
       </c>
       <c r="C99" s="17" t="s">
         <v>3</v>
@@ -7125,7 +7156,7 @@
         <v>47</v>
       </c>
       <c r="H99" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I99" s="17" t="s">
         <v>48</v>
@@ -7136,10 +7167,10 @@
     </row>
     <row r="100" spans="1:53" outlineLevel="2">
       <c r="A100" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="B100" s="17" t="s">
         <v>258</v>
-      </c>
-      <c r="B100" s="17" t="s">
-        <v>259</v>
       </c>
       <c r="C100" s="17" t="s">
         <v>3</v>
@@ -7157,7 +7188,7 @@
         <v>47</v>
       </c>
       <c r="H100" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I100" s="17" t="s">
         <v>48</v>
@@ -7167,10 +7198,10 @@
     </row>
     <row r="101" spans="1:53" outlineLevel="2">
       <c r="A101" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="B101" s="17" t="s">
         <v>260</v>
-      </c>
-      <c r="B101" s="17" t="s">
-        <v>261</v>
       </c>
       <c r="C101" s="17" t="s">
         <v>3</v>
@@ -7188,7 +7219,7 @@
         <v>47</v>
       </c>
       <c r="H101" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I101" s="17" t="s">
         <v>48</v>
@@ -7198,10 +7229,10 @@
     </row>
     <row r="102" spans="1:53" outlineLevel="2">
       <c r="A102" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="B102" s="17" t="s">
         <v>262</v>
-      </c>
-      <c r="B102" s="17" t="s">
-        <v>263</v>
       </c>
       <c r="C102" s="17" t="s">
         <v>3</v>
@@ -7219,7 +7250,7 @@
         <v>47</v>
       </c>
       <c r="H102" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I102" s="17" t="s">
         <v>48</v>
@@ -7229,10 +7260,10 @@
     </row>
     <row r="103" spans="1:53" outlineLevel="2">
       <c r="A103" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="B103" s="17" t="s">
         <v>264</v>
-      </c>
-      <c r="B103" s="17" t="s">
-        <v>265</v>
       </c>
       <c r="C103" s="17" t="s">
         <v>3</v>
@@ -7250,7 +7281,7 @@
         <v>47</v>
       </c>
       <c r="H103" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I103" s="17" t="s">
         <v>48</v>
@@ -7260,10 +7291,10 @@
     </row>
     <row r="104" spans="1:53" outlineLevel="2">
       <c r="A104" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="B104" s="17" t="s">
         <v>266</v>
-      </c>
-      <c r="B104" s="17" t="s">
-        <v>267</v>
       </c>
       <c r="C104" s="17" t="s">
         <v>3</v>
@@ -7275,26 +7306,26 @@
         <v>119</v>
       </c>
       <c r="F104" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G104" s="17" t="s">
         <v>47</v>
       </c>
       <c r="H104" s="17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I104" s="17" t="s">
         <v>48</v>
       </c>
       <c r="AL104" s="4"/>
-      <c r="AM104" s="21"/>
+      <c r="AM104" s="20"/>
     </row>
     <row r="105" spans="1:53" outlineLevel="2">
       <c r="A105" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="B105" s="17" t="s">
         <v>269</v>
-      </c>
-      <c r="B105" s="17" t="s">
-        <v>270</v>
       </c>
       <c r="C105" s="17" t="s">
         <v>3</v>
@@ -7320,10 +7351,10 @@
     </row>
     <row r="106" spans="1:53" outlineLevel="2">
       <c r="A106" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="B106" s="17" t="s">
         <v>271</v>
-      </c>
-      <c r="B106" s="17" t="s">
-        <v>272</v>
       </c>
       <c r="C106" s="17" t="s">
         <v>3</v>
@@ -7335,7 +7366,7 @@
         <v>119</v>
       </c>
       <c r="F106" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G106" s="17" t="s">
         <v>47</v>
@@ -7345,14 +7376,14 @@
         <v>48</v>
       </c>
       <c r="AL106" s="4"/>
-      <c r="AM106" s="21"/>
+      <c r="AM106" s="20"/>
     </row>
     <row r="107" spans="1:53" outlineLevel="2">
       <c r="A107" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="B107" s="17" t="s">
         <v>273</v>
-      </c>
-      <c r="B107" s="17" t="s">
-        <v>274</v>
       </c>
       <c r="C107" s="17" t="s">
         <v>3</v>
@@ -7361,10 +7392,10 @@
         <v>31</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F107" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G107" s="17" t="s">
         <v>82</v>
@@ -7373,14 +7404,14 @@
       <c r="I107" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="AM107" s="21"/>
+      <c r="AM107" s="20"/>
     </row>
     <row r="108" spans="1:53" outlineLevel="2">
       <c r="A108" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="B108" s="17" t="s">
         <v>275</v>
-      </c>
-      <c r="B108" s="17" t="s">
-        <v>276</v>
       </c>
       <c r="C108" s="17" t="s">
         <v>3</v>
@@ -7389,10 +7420,10 @@
         <v>31</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F108" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G108" s="17" t="s">
         <v>82</v>
@@ -7401,14 +7432,14 @@
       <c r="I108" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="AM108" s="21"/>
+      <c r="AM108" s="20"/>
     </row>
     <row r="109" spans="1:53" outlineLevel="2">
       <c r="A109" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="B109" s="17" t="s">
         <v>277</v>
-      </c>
-      <c r="B109" s="17" t="s">
-        <v>278</v>
       </c>
       <c r="C109" s="17" t="s">
         <v>3</v>
@@ -7417,10 +7448,10 @@
         <v>31</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F109" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G109" s="17" t="s">
         <v>82</v>
@@ -7429,26 +7460,26 @@
       <c r="I109" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="AM109" s="21"/>
+      <c r="AM109" s="20"/>
     </row>
     <row r="110" spans="1:53" outlineLevel="2">
       <c r="A110" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="B110" s="17" t="s">
         <v>279</v>
-      </c>
-      <c r="B110" s="17" t="s">
-        <v>280</v>
       </c>
       <c r="C110" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D110" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="E110" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="F110" s="17" t="s">
         <v>281</v>
-      </c>
-      <c r="E110" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="F110" s="17" t="s">
-        <v>282</v>
       </c>
       <c r="G110" s="17" t="s">
         <v>136</v>
@@ -7467,19 +7498,19 @@
     </row>
     <row r="111" spans="1:53" outlineLevel="2">
       <c r="A111" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="B111" s="17" t="s">
         <v>283</v>
-      </c>
-      <c r="B111" s="17" t="s">
-        <v>284</v>
       </c>
       <c r="C111" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F111" s="17" t="s">
         <v>135</v>
@@ -7505,22 +7536,22 @@
     </row>
     <row r="112" spans="1:53" outlineLevel="2">
       <c r="A112" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="B112" s="17" t="s">
         <v>285</v>
-      </c>
-      <c r="B112" s="17" t="s">
-        <v>286</v>
       </c>
       <c r="C112" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F112" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G112" s="17" t="s">
         <v>136</v>
@@ -7547,22 +7578,22 @@
     </row>
     <row r="113" spans="1:62" outlineLevel="2">
       <c r="A113" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="B113" s="17" t="s">
         <v>288</v>
-      </c>
-      <c r="B113" s="17" t="s">
-        <v>289</v>
       </c>
       <c r="C113" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F113" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G113" s="17" t="s">
         <v>136</v>
@@ -7593,22 +7624,22 @@
     </row>
     <row r="114" spans="1:62" outlineLevel="2">
       <c r="A114" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B114" s="17" t="s">
         <v>291</v>
-      </c>
-      <c r="B114" s="17" t="s">
-        <v>292</v>
       </c>
       <c r="C114" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F114" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G114" s="17" t="s">
         <v>136</v>
@@ -7641,22 +7672,22 @@
     </row>
     <row r="115" spans="1:62" outlineLevel="2">
       <c r="A115" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="B115" s="17" t="s">
         <v>294</v>
-      </c>
-      <c r="B115" s="17" t="s">
-        <v>295</v>
       </c>
       <c r="C115" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F115" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G115" s="17" t="s">
         <v>136</v>
@@ -7692,7 +7723,7 @@
     </row>
     <row r="116" spans="1:62">
       <c r="A116" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
@@ -7706,7 +7737,7 @@
     </row>
     <row r="117" spans="1:62" outlineLevel="1">
       <c r="A117" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B117" s="10"/>
       <c r="C117" s="10"/>
@@ -7720,10 +7751,10 @@
     </row>
     <row r="118" spans="1:62" outlineLevel="2">
       <c r="A118" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B118" s="17" t="s">
         <v>299</v>
-      </c>
-      <c r="B118" s="17" t="s">
-        <v>300</v>
       </c>
       <c r="C118" s="17" t="s">
         <v>3</v>
@@ -7738,7 +7769,7 @@
         <v>67</v>
       </c>
       <c r="G118" s="17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H118" s="17"/>
       <c r="I118" s="17" t="s">
@@ -7749,10 +7780,10 @@
     </row>
     <row r="119" spans="1:62" outlineLevel="2">
       <c r="A119" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="B119" s="17" t="s">
         <v>302</v>
-      </c>
-      <c r="B119" s="17" t="s">
-        <v>303</v>
       </c>
       <c r="C119" s="17" t="s">
         <v>3</v>
@@ -7767,7 +7798,7 @@
         <v>67</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H119" s="17"/>
       <c r="I119" s="17" t="s">
@@ -7778,10 +7809,10 @@
     </row>
     <row r="120" spans="1:62" outlineLevel="2">
       <c r="A120" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="B120" s="17" t="s">
         <v>304</v>
-      </c>
-      <c r="B120" s="17" t="s">
-        <v>305</v>
       </c>
       <c r="C120" s="17" t="s">
         <v>6</v>
@@ -7790,21 +7821,21 @@
         <v>31</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="F120" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G120" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="H120" s="17" t="s">
         <v>306</v>
-      </c>
-      <c r="H120" s="17" t="s">
-        <v>307</v>
       </c>
       <c r="I120" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="AM120" s="20"/>
+      <c r="AM120" s="21"/>
       <c r="AN120" s="6"/>
       <c r="AO120" s="6"/>
       <c r="AP120" s="6"/>
@@ -7817,10 +7848,10 @@
     </row>
     <row r="121" spans="1:62" outlineLevel="2">
       <c r="A121" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="B121" s="17" t="s">
         <v>308</v>
-      </c>
-      <c r="B121" s="17" t="s">
-        <v>309</v>
       </c>
       <c r="C121" s="17" t="s">
         <v>6</v>
@@ -7835,10 +7866,10 @@
         <v>126</v>
       </c>
       <c r="G121" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="H121" s="17" t="s">
         <v>310</v>
-      </c>
-      <c r="H121" s="17" t="s">
-        <v>311</v>
       </c>
       <c r="I121" s="17" t="s">
         <v>48</v>
@@ -7848,7 +7879,7 @@
       <c r="AJ121" s="7"/>
       <c r="AK121" s="7"/>
       <c r="AL121" s="7"/>
-      <c r="AM121" s="20"/>
+      <c r="AM121" s="21"/>
       <c r="AN121" s="6"/>
       <c r="AO121" s="6"/>
       <c r="AP121" s="6"/>
@@ -7873,10 +7904,10 @@
     </row>
     <row r="122" spans="1:62" outlineLevel="2">
       <c r="A122" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="B122" s="17" t="s">
         <v>312</v>
-      </c>
-      <c r="B122" s="17" t="s">
-        <v>313</v>
       </c>
       <c r="C122" s="17" t="s">
         <v>6</v>
@@ -7888,24 +7919,24 @@
         <v>46</v>
       </c>
       <c r="F122" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="G122" s="17" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="H122" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I122" s="17" t="s">
         <v>48</v>
       </c>
       <c r="AK122" s="7"/>
       <c r="AL122" s="7"/>
-      <c r="AM122" s="20"/>
+      <c r="AM122" s="21"/>
     </row>
     <row r="123" spans="1:62">
       <c r="A123" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B123" s="15"/>
       <c r="C123" s="15"/>
@@ -7919,7 +7950,7 @@
     </row>
     <row r="124" spans="1:62" outlineLevel="1">
       <c r="A124" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B124" s="10"/>
       <c r="C124" s="10"/>
@@ -7933,10 +7964,10 @@
     </row>
     <row r="125" spans="1:62" outlineLevel="2">
       <c r="A125" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="B125" s="17" t="s">
         <v>316</v>
-      </c>
-      <c r="B125" s="17" t="s">
-        <v>317</v>
       </c>
       <c r="C125" s="17" t="s">
         <v>3</v>
@@ -7954,7 +7985,7 @@
         <v>47</v>
       </c>
       <c r="H125" s="17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I125" s="17" t="s">
         <v>48</v>
@@ -7965,10 +7996,10 @@
     </row>
     <row r="126" spans="1:62" outlineLevel="2">
       <c r="A126" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="B126" s="17" t="s">
         <v>319</v>
-      </c>
-      <c r="B126" s="17" t="s">
-        <v>320</v>
       </c>
       <c r="C126" s="17" t="s">
         <v>4</v>
@@ -7980,7 +8011,7 @@
         <v>67</v>
       </c>
       <c r="F126" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G126" s="17" t="s">
         <v>136</v>
@@ -8000,10 +8031,10 @@
     </row>
     <row r="127" spans="1:62" outlineLevel="2">
       <c r="A127" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="B127" s="17" t="s">
         <v>322</v>
-      </c>
-      <c r="B127" s="17" t="s">
-        <v>323</v>
       </c>
       <c r="C127" s="17" t="s">
         <v>3</v>
@@ -8015,7 +8046,7 @@
         <v>67</v>
       </c>
       <c r="F127" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G127" s="17" t="s">
         <v>47</v>
@@ -8027,14 +8058,14 @@
       <c r="AJ127" s="4"/>
       <c r="AK127" s="4"/>
       <c r="AL127" s="4"/>
-      <c r="AM127" s="21"/>
+      <c r="AM127" s="20"/>
     </row>
     <row r="128" spans="1:62" outlineLevel="2">
       <c r="A128" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="B128" s="17" t="s">
         <v>324</v>
-      </c>
-      <c r="B128" s="17" t="s">
-        <v>325</v>
       </c>
       <c r="C128" s="17" t="s">
         <v>3</v>
@@ -8049,7 +8080,7 @@
         <v>67</v>
       </c>
       <c r="G128" s="17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H128" s="17"/>
       <c r="I128" s="17" t="s">
@@ -8060,13 +8091,13 @@
     </row>
     <row r="129" spans="1:62" outlineLevel="2">
       <c r="A129" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="B129" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="B129" s="17" t="s">
-        <v>328</v>
-      </c>
       <c r="C129" s="17" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D129" s="17" t="s">
         <v>31</v>
@@ -8078,31 +8109,29 @@
         <v>146</v>
       </c>
       <c r="G129" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="H129" s="17" t="s">
-        <v>318</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="H129" s="17"/>
       <c r="I129" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="AD129" s="7"/>
-      <c r="AE129" s="7"/>
-      <c r="AF129" s="7"/>
-      <c r="AG129" s="7"/>
-      <c r="AH129" s="7"/>
-      <c r="AI129" s="7"/>
-      <c r="AJ129" s="7"/>
-      <c r="AK129" s="7"/>
-      <c r="AL129" s="7"/>
+      <c r="AD129" s="4"/>
+      <c r="AE129" s="4"/>
+      <c r="AF129" s="4"/>
+      <c r="AG129" s="4"/>
+      <c r="AH129" s="4"/>
+      <c r="AI129" s="4"/>
+      <c r="AJ129" s="4"/>
+      <c r="AK129" s="4"/>
+      <c r="AL129" s="4"/>
       <c r="AM129" s="20"/>
     </row>
     <row r="130" spans="1:62" outlineLevel="2">
       <c r="A130" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="B130" s="17" t="s">
         <v>329</v>
-      </c>
-      <c r="B130" s="17" t="s">
-        <v>330</v>
       </c>
       <c r="C130" s="17" t="s">
         <v>5</v>
@@ -8114,10 +8143,10 @@
         <v>70</v>
       </c>
       <c r="F130" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="G130" s="17" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="H130" s="17"/>
       <c r="I130" s="17" t="s">
@@ -8127,7 +8156,7 @@
     </row>
     <row r="131" spans="1:62" outlineLevel="1">
       <c r="A131" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B131" s="10"/>
       <c r="C131" s="10"/>
@@ -8141,13 +8170,13 @@
     </row>
     <row r="132" spans="1:62" outlineLevel="2">
       <c r="A132" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B132" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="B132" s="17" t="s">
+      <c r="C132" s="17" t="s">
         <v>333</v>
-      </c>
-      <c r="C132" s="17" t="s">
-        <v>334</v>
       </c>
       <c r="D132" s="17" t="s">
         <v>31</v>
@@ -8156,10 +8185,10 @@
         <v>67</v>
       </c>
       <c r="F132" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="G132" s="17" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="H132" s="17"/>
       <c r="I132" s="17" t="s">
@@ -8172,13 +8201,13 @@
     </row>
     <row r="133" spans="1:62" outlineLevel="2">
       <c r="A133" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="B133" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="B133" s="17" t="s">
-        <v>336</v>
-      </c>
       <c r="C133" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D133" s="17" t="s">
         <v>31</v>
@@ -8187,10 +8216,10 @@
         <v>67</v>
       </c>
       <c r="F133" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="G133" s="17" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="H133" s="17"/>
       <c r="I133" s="17" t="s">
@@ -8203,13 +8232,13 @@
     </row>
     <row r="134" spans="1:62" outlineLevel="2">
       <c r="A134" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="B134" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="B134" s="17" t="s">
-        <v>338</v>
-      </c>
       <c r="C134" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D134" s="17" t="s">
         <v>31</v>
@@ -8218,10 +8247,10 @@
         <v>67</v>
       </c>
       <c r="F134" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="G134" s="17" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="H134" s="17"/>
       <c r="I134" s="17" t="s">
@@ -8234,13 +8263,13 @@
     </row>
     <row r="135" spans="1:62" outlineLevel="2">
       <c r="A135" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="B135" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="B135" s="17" t="s">
-        <v>340</v>
-      </c>
       <c r="C135" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D135" s="17" t="s">
         <v>31</v>
@@ -8249,10 +8278,10 @@
         <v>67</v>
       </c>
       <c r="F135" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="H135" s="17"/>
       <c r="I135" s="17" t="s">
@@ -8265,7 +8294,7 @@
     </row>
     <row r="136" spans="1:62">
       <c r="A136" s="15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
@@ -8279,7 +8308,7 @@
     </row>
     <row r="137" spans="1:62" outlineLevel="1">
       <c r="A137" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B137" s="10"/>
       <c r="C137" s="10"/>
@@ -8293,16 +8322,16 @@
     </row>
     <row r="138" spans="1:62" outlineLevel="2">
       <c r="A138" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="B138" s="17" t="s">
         <v>343</v>
-      </c>
-      <c r="B138" s="17" t="s">
-        <v>344</v>
       </c>
       <c r="C138" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E138" s="17" t="s">
         <v>77</v>
@@ -8311,11 +8340,11 @@
         <v>77</v>
       </c>
       <c r="G138" s="17" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H138" s="17"/>
       <c r="I138" s="17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AH138" s="13" t="s">
         <v>24</v>
@@ -8324,31 +8353,31 @@
     </row>
     <row r="139" spans="1:62" outlineLevel="2">
       <c r="A139" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="B139" s="17" t="s">
         <v>348</v>
-      </c>
-      <c r="B139" s="17" t="s">
-        <v>349</v>
       </c>
       <c r="C139" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D139" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="E139" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F139" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="G139" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="E139" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="F139" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="G139" s="17" t="s">
+      <c r="H139" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="I139" s="17" t="s">
         <v>346</v>
-      </c>
-      <c r="H139" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="I139" s="17" t="s">
-        <v>347</v>
       </c>
       <c r="AM139" s="16"/>
       <c r="AV139" s="13" t="s">
@@ -8357,31 +8386,31 @@
     </row>
     <row r="140" spans="1:62" outlineLevel="2">
       <c r="A140" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="B140" s="17" t="s">
         <v>351</v>
-      </c>
-      <c r="B140" s="17" t="s">
-        <v>352</v>
       </c>
       <c r="C140" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D140" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="E140" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="F140" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="G140" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="E140" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="F140" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="G140" s="17" t="s">
+      <c r="H140" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I140" s="17" t="s">
         <v>346</v>
-      </c>
-      <c r="H140" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="I140" s="17" t="s">
-        <v>347</v>
       </c>
       <c r="AM140" s="16"/>
       <c r="BJ140" s="13" t="s">
@@ -8390,7 +8419,7 @@
     </row>
     <row r="141" spans="1:62" outlineLevel="1">
       <c r="A141" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B141" s="10"/>
       <c r="C141" s="10"/>
@@ -8404,29 +8433,29 @@
     </row>
     <row r="142" spans="1:62" outlineLevel="2">
       <c r="A142" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="B142" s="17" t="s">
         <v>354</v>
-      </c>
-      <c r="B142" s="17" t="s">
-        <v>355</v>
       </c>
       <c r="C142" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D142" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="E142" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="F142" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="G142" s="17" t="s">
         <v>356</v>
-      </c>
-      <c r="E142" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="F142" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="G142" s="17" t="s">
-        <v>357</v>
       </c>
       <c r="H142" s="17"/>
       <c r="I142" s="17" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM142" s="16"/>
       <c r="AQ142" s="13" t="s">
@@ -8435,29 +8464,29 @@
     </row>
     <row r="143" spans="1:62" outlineLevel="2">
       <c r="A143" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="B143" s="17" t="s">
         <v>359</v>
-      </c>
-      <c r="B143" s="17" t="s">
-        <v>360</v>
       </c>
       <c r="C143" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E143" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F143" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G143" s="17" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H143" s="17"/>
       <c r="I143" s="17" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM143" s="14" t="s">
         <v>24</v>
@@ -8465,7 +8494,7 @@
     </row>
     <row r="144" spans="1:62" outlineLevel="1">
       <c r="A144" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B144" s="10"/>
       <c r="C144" s="10"/>
@@ -8479,25 +8508,25 @@
     </row>
     <row r="145" spans="1:82" outlineLevel="2">
       <c r="A145" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="B145" s="17" t="s">
         <v>363</v>
-      </c>
-      <c r="B145" s="17" t="s">
-        <v>364</v>
       </c>
       <c r="C145" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E145" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="F145" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="G145" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H145" s="17"/>
       <c r="I145" s="17" t="s">
@@ -8507,10 +8536,10 @@
     </row>
     <row r="146" spans="1:82" outlineLevel="2">
       <c r="A146" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="B146" s="17" t="s">
         <v>365</v>
-      </c>
-      <c r="B146" s="17" t="s">
-        <v>366</v>
       </c>
       <c r="C146" s="17" t="s">
         <v>5</v>
@@ -8519,17 +8548,17 @@
         <v>31</v>
       </c>
       <c r="E146" s="17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F146" s="17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G146" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H146" s="17"/>
       <c r="I146" s="17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AM146" s="16"/>
       <c r="BK146" s="6"/>
@@ -8542,29 +8571,29 @@
     </row>
     <row r="147" spans="1:82" outlineLevel="2">
       <c r="A147" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="B147" s="17" t="s">
         <v>368</v>
-      </c>
-      <c r="B147" s="17" t="s">
-        <v>369</v>
       </c>
       <c r="C147" s="17" t="s">
         <v>5</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E147" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="F147" s="17" t="s">
         <v>370</v>
       </c>
-      <c r="F147" s="17" t="s">
-        <v>371</v>
-      </c>
       <c r="G147" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H147" s="17"/>
       <c r="I147" s="17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AM147" s="16"/>
       <c r="BR147" s="6"/>
@@ -8577,10 +8606,10 @@
     </row>
     <row r="148" spans="1:82" outlineLevel="2">
       <c r="A148" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="B148" s="17" t="s">
         <v>372</v>
-      </c>
-      <c r="B148" s="17" t="s">
-        <v>373</v>
       </c>
       <c r="C148" s="17" t="s">
         <v>5</v>
@@ -8589,17 +8618,17 @@
         <v>31</v>
       </c>
       <c r="E148" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="F148" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="F148" s="17" t="s">
-        <v>375</v>
-      </c>
       <c r="G148" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H148" s="17"/>
       <c r="I148" s="17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AM148" s="16"/>
       <c r="BY148" s="6"/>
@@ -8638,31 +8667,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -8670,13 +8699,13 @@
         <v>33</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
@@ -8684,10 +8713,10 @@
         <v>2</v>
       </c>
       <c r="H2" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="I2" s="17" t="s">
         <v>387</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -8695,13 +8724,13 @@
         <v>38</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E3" s="17"/>
       <c r="F3" s="17"/>
@@ -8709,24 +8738,24 @@
         <v>20</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="17" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E4" s="17"/>
       <c r="F4" s="17"/>
@@ -8734,10 +8763,10 @@
         <v>8</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -8745,13 +8774,13 @@
         <v>41</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="17"/>
@@ -8759,24 +8788,24 @@
         <v>1</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="17" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>42</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E6" s="17"/>
       <c r="F6" s="17"/>
@@ -8784,24 +8813,24 @@
         <v>1</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>398</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>395</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>399</v>
       </c>
       <c r="E7" s="17"/>
       <c r="F7" s="17"/>
@@ -8809,24 +8838,24 @@
         <v>1</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>398</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>395</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>399</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="17"/>
@@ -8834,10 +8863,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -8845,13 +8874,13 @@
         <v>52</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>42</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E9" s="17"/>
       <c r="F9" s="17"/>
@@ -8859,10 +8888,10 @@
         <v>12</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -8870,13 +8899,13 @@
         <v>52</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="17"/>
@@ -8884,10 +8913,10 @@
         <v>1</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -8895,13 +8924,13 @@
         <v>52</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
@@ -8909,10 +8938,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -8920,13 +8949,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C12" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>406</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>407</v>
       </c>
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
@@ -8934,10 +8963,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -8945,13 +8974,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>42</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
@@ -8959,10 +8988,10 @@
         <v>6</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -8970,13 +8999,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>42</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
@@ -8984,10 +9013,10 @@
         <v>19</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -8995,13 +9024,13 @@
         <v>60</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
@@ -9009,10 +9038,10 @@
         <v>1</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -9020,13 +9049,13 @@
         <v>77</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>42</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
@@ -9034,10 +9063,10 @@
         <v>3</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -9045,26 +9074,26 @@
         <v>70</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>42</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E17" s="17"/>
       <c r="F17" s="17" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G17" s="17">
         <v>8</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -9072,26 +9101,26 @@
         <v>67</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>42</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E18" s="17"/>
       <c r="F18" s="17" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G18" s="17">
         <v>19</v>
       </c>
       <c r="H18" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="I18" s="17" t="s">
         <v>424</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -9099,13 +9128,13 @@
         <v>67</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
@@ -9113,10 +9142,10 @@
         <v>18</v>
       </c>
       <c r="H19" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="I19" s="17" t="s">
         <v>427</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -9124,13 +9153,13 @@
         <v>67</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
@@ -9138,10 +9167,10 @@
         <v>7</v>
       </c>
       <c r="H20" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="I20" s="17" t="s">
         <v>430</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -9149,13 +9178,13 @@
         <v>67</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
@@ -9163,10 +9192,10 @@
         <v>6</v>
       </c>
       <c r="H21" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="I21" s="17" t="s">
         <v>433</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -9174,26 +9203,26 @@
         <v>67</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D22" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="E22" s="17" t="s">
         <v>435</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>436</v>
       </c>
       <c r="F22" s="17"/>
       <c r="G22" s="17">
         <v>4</v>
       </c>
       <c r="H22" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="I22" s="17" t="s">
         <v>437</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -9201,26 +9230,26 @@
         <v>46</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>42</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E23" s="17"/>
       <c r="F23" s="17" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G23" s="17">
         <v>9</v>
       </c>
       <c r="H23" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="I23" s="17" t="s">
         <v>441</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -9228,28 +9257,28 @@
         <v>46</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D24" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>443</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="F24" s="17" t="s">
         <v>444</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>445</v>
       </c>
       <c r="G24" s="17">
         <v>14</v>
       </c>
       <c r="H24" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="I24" s="17" t="s">
         <v>446</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -9257,28 +9286,28 @@
         <v>46</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D25" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>448</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="F25" s="17" t="s">
         <v>449</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>450</v>
       </c>
       <c r="G25" s="17">
         <v>14</v>
       </c>
       <c r="H25" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="I25" s="17" t="s">
         <v>451</v>
-      </c>
-      <c r="I25" s="17" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -9286,13 +9315,13 @@
         <v>46</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
@@ -9300,10 +9329,10 @@
         <v>3</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -9311,16 +9340,16 @@
         <v>46</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D27" s="17" t="s">
+        <v>454</v>
+      </c>
+      <c r="E27" s="17" t="s">
         <v>455</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>456</v>
       </c>
       <c r="F27" s="17"/>
       <c r="G27" s="17">
@@ -9328,7 +9357,7 @@
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -9336,13 +9365,13 @@
         <v>119</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
@@ -9350,10 +9379,10 @@
         <v>12</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -9361,13 +9390,13 @@
         <v>119</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -9375,10 +9404,10 @@
         <v>6</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -9386,26 +9415,26 @@
         <v>119</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G30" s="17">
         <v>6</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -9413,13 +9442,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
@@ -9427,10 +9456,10 @@
         <v>1</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -9438,16 +9467,16 @@
         <v>119</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D32" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="E32" s="17" t="s">
         <v>467</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>468</v>
       </c>
       <c r="F32" s="17"/>
       <c r="G32" s="17">
@@ -9455,108 +9484,108 @@
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>42</v>
       </c>
       <c r="D33" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="E33" s="17" t="s">
         <v>470</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="F33" s="17" t="s">
         <v>471</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="G33" s="17">
+        <v>13</v>
+      </c>
+      <c r="H33" s="17" t="s">
         <v>472</v>
       </c>
-      <c r="G33" s="17">
-        <v>11</v>
-      </c>
-      <c r="H33" s="17" t="s">
+      <c r="I33" s="17" t="s">
         <v>473</v>
-      </c>
-      <c r="I33" s="17" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D34" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="E34" s="17" t="s">
         <v>475</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="F34" s="17" t="s">
         <v>476</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="G34" s="17">
+        <v>6</v>
+      </c>
+      <c r="H34" s="17" t="s">
         <v>477</v>
       </c>
-      <c r="G34" s="17">
-        <v>5</v>
-      </c>
-      <c r="H34" s="17" t="s">
+      <c r="I34" s="17" t="s">
         <v>478</v>
-      </c>
-      <c r="I34" s="17" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D35" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="E35" s="17" t="s">
         <v>480</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="F35" s="17" t="s">
         <v>481</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="G35" s="17">
+        <v>14</v>
+      </c>
+      <c r="H35" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G35" s="17">
-        <v>12</v>
-      </c>
-      <c r="H35" s="17" t="s">
+      <c r="I35" s="17" t="s">
         <v>483</v>
-      </c>
-      <c r="I35" s="17" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="17"/>
@@ -9564,37 +9593,37 @@
         <v>5</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D37" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="E37" s="17" t="s">
         <v>487</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>488</v>
       </c>
       <c r="F37" s="17"/>
       <c r="G37" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="I37" s="17" t="s">
         <v>489</v>
-      </c>
-      <c r="I37" s="17" t="s">
-        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -9605,7 +9634,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -9618,53 +9647,53 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>496</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="D2" s="17" t="s">
         <v>497</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="E2" s="17" t="s">
-        <v>499</v>
-      </c>
       <c r="F2" s="17">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B3" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>500</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>489</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>501</v>
@@ -9673,12 +9702,12 @@
         <v>502</v>
       </c>
       <c r="F3" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>503</v>
@@ -9693,12 +9722,12 @@
         <v>506</v>
       </c>
       <c r="F4" s="17">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>507</v>
@@ -9707,27 +9736,27 @@
         <v>508</v>
       </c>
       <c r="D5" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>509</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>510</v>
-      </c>
       <c r="F5" s="17">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B6" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>511</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>512</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>498</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>513</v>
@@ -9738,7 +9767,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>514</v>
@@ -9747,18 +9776,18 @@
         <v>515</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>516</v>
       </c>
       <c r="F7" s="17">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>517</v>
@@ -9767,218 +9796,218 @@
         <v>518</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F8" s="17">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F9" s="17">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F10" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F11" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F12" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F13" s="17">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F14" s="17">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F15" s="17">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F16" s="17">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>548</v>
+        <v>519</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>549</v>
       </c>
       <c r="F17" s="17">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B18" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>550</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="D18" s="17" t="s">
         <v>551</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>544</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>552</v>
       </c>
       <c r="F18" s="17">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>553</v>
@@ -9987,18 +10016,18 @@
         <v>554</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>555</v>
       </c>
       <c r="F19" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>556</v>
@@ -10007,58 +10036,58 @@
         <v>557</v>
       </c>
       <c r="D20" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>558</v>
       </c>
-      <c r="E20" s="17" t="s">
-        <v>559</v>
-      </c>
       <c r="F20" s="17">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B21" s="17" t="s">
+        <v>559</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>560</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="D21" s="17" t="s">
         <v>561</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>498</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>562</v>
       </c>
       <c r="F21" s="17">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="17" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>563</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>466</v>
+        <v>564</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>564</v>
+        <v>505</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>565</v>
       </c>
       <c r="F22" s="17">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="17" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>566</v>
@@ -10067,18 +10096,18 @@
         <v>567</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>544</v>
+        <v>505</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>568</v>
       </c>
       <c r="F23" s="17">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="17" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>569</v>
@@ -10087,33 +10116,33 @@
         <v>570</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F24" s="17">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="17" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F25" s="17">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -10121,19 +10150,19 @@
         <v>119</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>575</v>
+        <v>465</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F26" s="17">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -10141,19 +10170,19 @@
         <v>119</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F27" s="17">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -10161,19 +10190,19 @@
         <v>119</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>583</v>
+        <v>523</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>584</v>
       </c>
       <c r="F28" s="17">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -10187,13 +10216,13 @@
         <v>586</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>583</v>
+        <v>523</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>587</v>
       </c>
       <c r="F29" s="17">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -10201,19 +10230,19 @@
         <v>119</v>
       </c>
       <c r="B30" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="C30" s="17" t="s">
         <v>588</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="D30" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>589</v>
       </c>
-      <c r="D30" s="17" t="s">
-        <v>498</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>590</v>
-      </c>
       <c r="F30" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -10221,19 +10250,19 @@
         <v>119</v>
       </c>
       <c r="B31" s="17" t="s">
+        <v>590</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>591</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="D31" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>592</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>583</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>593</v>
-      </c>
       <c r="F31" s="17">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -10241,19 +10270,19 @@
         <v>119</v>
       </c>
       <c r="B32" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>594</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="D32" s="17" t="s">
         <v>595</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>509</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>596</v>
       </c>
       <c r="F32" s="17">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -10267,13 +10296,13 @@
         <v>598</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>576</v>
+        <v>595</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>599</v>
       </c>
       <c r="F33" s="17">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -10287,18 +10316,18 @@
         <v>601</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>544</v>
+        <v>512</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>602</v>
       </c>
       <c r="F34" s="17">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="17" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="B35" s="17" t="s">
         <v>603</v>
@@ -10307,18 +10336,18 @@
         <v>604</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>544</v>
+        <v>595</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>605</v>
       </c>
       <c r="F35" s="17">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="17" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>606</v>
@@ -10327,18 +10356,18 @@
         <v>607</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="E36" s="17" t="s">
         <v>608</v>
       </c>
       <c r="F36" s="17">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="17" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>609</v>
@@ -10347,18 +10376,18 @@
         <v>610</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>576</v>
+        <v>497</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>611</v>
       </c>
       <c r="F37" s="17">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="17" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>612</v>
@@ -10367,13 +10396,13 @@
         <v>613</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>576</v>
+        <v>505</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>614</v>
       </c>
       <c r="F38" s="17">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -10387,13 +10416,13 @@
         <v>616</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>564</v>
+        <v>505</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>617</v>
       </c>
       <c r="F39" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -10407,13 +10436,13 @@
         <v>619</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>564</v>
+        <v>512</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>620</v>
       </c>
       <c r="F40" s="17">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -10427,7 +10456,7 @@
         <v>622</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>564</v>
+        <v>497</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>623</v>
@@ -10447,13 +10476,13 @@
         <v>625</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>548</v>
+        <v>497</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>626</v>
       </c>
       <c r="F42" s="17">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -10467,13 +10496,13 @@
         <v>628</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>548</v>
+        <v>577</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>629</v>
       </c>
       <c r="F43" s="17">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -10487,13 +10516,13 @@
         <v>631</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>548</v>
+        <v>577</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>632</v>
       </c>
       <c r="F44" s="17">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -10507,13 +10536,13 @@
         <v>634</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>498</v>
+        <v>577</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>635</v>
       </c>
       <c r="F45" s="17">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -10527,13 +10556,13 @@
         <v>637</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>638</v>
       </c>
       <c r="F46" s="17">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -10547,13 +10576,13 @@
         <v>640</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>498</v>
+        <v>561</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>641</v>
       </c>
       <c r="F47" s="17">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -10567,13 +10596,13 @@
         <v>643</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>644</v>
       </c>
       <c r="F48" s="17">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -10587,13 +10616,13 @@
         <v>646</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>583</v>
+        <v>512</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>647</v>
       </c>
       <c r="F49" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -10607,13 +10636,13 @@
         <v>649</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>650</v>
       </c>
       <c r="F50" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -10627,13 +10656,13 @@
         <v>652</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>548</v>
+        <v>512</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>653</v>
       </c>
       <c r="F51" s="17">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -10647,13 +10676,13 @@
         <v>655</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>544</v>
+        <v>571</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>656</v>
       </c>
       <c r="F52" s="17">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -10667,18 +10696,18 @@
         <v>658</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>659</v>
       </c>
       <c r="F53" s="17">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="17" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B54" s="17" t="s">
         <v>660</v>
@@ -10687,18 +10716,18 @@
         <v>661</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>662</v>
       </c>
       <c r="F54" s="17">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="17" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B55" s="17" t="s">
         <v>663</v>
@@ -10707,18 +10736,18 @@
         <v>664</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>665</v>
       </c>
       <c r="F55" s="17">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="17" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B56" s="17" t="s">
         <v>666</v>
@@ -10727,18 +10756,18 @@
         <v>667</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>668</v>
       </c>
       <c r="F56" s="17">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="17" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B57" s="17" t="s">
         <v>669</v>
@@ -10747,13 +10776,13 @@
         <v>670</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>509</v>
+        <v>595</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>671</v>
       </c>
       <c r="F57" s="17">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -10767,13 +10796,13 @@
         <v>673</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>558</v>
+        <v>595</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>674</v>
       </c>
       <c r="F58" s="17">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -10787,13 +10816,13 @@
         <v>676</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>498</v>
+        <v>595</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>677</v>
       </c>
       <c r="F59" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -10807,13 +10836,13 @@
         <v>679</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>548</v>
+        <v>523</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>680</v>
       </c>
       <c r="F60" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -10827,13 +10856,13 @@
         <v>682</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>548</v>
+        <v>523</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>683</v>
       </c>
       <c r="F61" s="17">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -10847,13 +10876,13 @@
         <v>685</v>
       </c>
       <c r="D62" s="17" t="s">
+        <v>571</v>
+      </c>
+      <c r="E62" s="17" t="s">
         <v>686</v>
       </c>
-      <c r="E62" s="17" t="s">
-        <v>687</v>
-      </c>
       <c r="F62" s="17">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -10861,19 +10890,19 @@
         <v>67</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C63" s="17" t="s">
         <v>688</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>297</v>
+        <v>512</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>689</v>
       </c>
       <c r="F63" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -10887,13 +10916,13 @@
         <v>691</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>509</v>
+        <v>561</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>692</v>
       </c>
       <c r="F64" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -10907,13 +10936,13 @@
         <v>694</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>501</v>
+        <v>561</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>695</v>
       </c>
       <c r="F65" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -10927,13 +10956,13 @@
         <v>697</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>558</v>
+        <v>698</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F66" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -10941,13 +10970,13 @@
         <v>67</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C67" s="17" t="s">
         <v>700</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>548</v>
+        <v>296</v>
       </c>
       <c r="E67" s="17" t="s">
         <v>701</v>
@@ -10961,19 +10990,19 @@
         <v>67</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>548</v>
+        <v>523</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F68" s="17">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -10981,19 +11010,19 @@
         <v>67</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F69" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -11001,16 +11030,16 @@
         <v>67</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="F70" s="17">
         <v>2</v>
@@ -11021,19 +11050,19 @@
         <v>67</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>711</v>
+        <v>561</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F71" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -11041,19 +11070,19 @@
         <v>67</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C72" s="17" t="s">
         <v>714</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>686</v>
+        <v>561</v>
       </c>
       <c r="E72" s="17" t="s">
         <v>715</v>
       </c>
       <c r="F72" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -11061,19 +11090,19 @@
         <v>67</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F73" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -11081,19 +11110,19 @@
         <v>67</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C74" s="17" t="s">
         <v>719</v>
       </c>
       <c r="D74" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="E74" s="17" t="s">
         <v>720</v>
       </c>
-      <c r="E74" s="17" t="s">
-        <v>721</v>
-      </c>
       <c r="F74" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -11101,19 +11130,19 @@
         <v>67</v>
       </c>
       <c r="B75" s="17" t="s">
+        <v>721</v>
+      </c>
+      <c r="C75" s="17" t="s">
         <v>722</v>
       </c>
-      <c r="C75" s="17" t="s">
+      <c r="D75" s="17" t="s">
         <v>723</v>
-      </c>
-      <c r="D75" s="17" t="s">
-        <v>509</v>
       </c>
       <c r="E75" s="17" t="s">
         <v>724</v>
       </c>
       <c r="F75" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -11127,13 +11156,13 @@
         <v>726</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>509</v>
+        <v>698</v>
       </c>
       <c r="E76" s="17" t="s">
         <v>727</v>
       </c>
       <c r="F76" s="17">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -11141,19 +11170,19 @@
         <v>67</v>
       </c>
       <c r="B77" s="17" t="s">
+        <v>725</v>
+      </c>
+      <c r="C77" s="17" t="s">
         <v>728</v>
       </c>
-      <c r="C77" s="17" t="s">
+      <c r="D77" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="E77" s="17" t="s">
         <v>729</v>
       </c>
-      <c r="D77" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="E77" s="17" t="s">
-        <v>730</v>
-      </c>
       <c r="F77" s="17">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -11161,19 +11190,19 @@
         <v>67</v>
       </c>
       <c r="B78" s="17" t="s">
+        <v>730</v>
+      </c>
+      <c r="C78" s="17" t="s">
         <v>731</v>
       </c>
-      <c r="C78" s="17" t="s">
+      <c r="D78" s="17" t="s">
         <v>732</v>
-      </c>
-      <c r="D78" s="17" t="s">
-        <v>558</v>
       </c>
       <c r="E78" s="17" t="s">
         <v>733</v>
       </c>
       <c r="F78" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -11187,7 +11216,7 @@
         <v>735</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="E79" s="17" t="s">
         <v>736</v>
@@ -11207,13 +11236,13 @@
         <v>738</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>558</v>
+        <v>523</v>
       </c>
       <c r="E80" s="17" t="s">
         <v>739</v>
       </c>
       <c r="F80" s="17">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -11227,13 +11256,13 @@
         <v>741</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>509</v>
+        <v>296</v>
       </c>
       <c r="E81" s="17" t="s">
         <v>742</v>
       </c>
       <c r="F81" s="17">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -11247,13 +11276,13 @@
         <v>744</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="E82" s="17" t="s">
         <v>745</v>
       </c>
       <c r="F82" s="17">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -11267,7 +11296,7 @@
         <v>747</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>558</v>
+        <v>512</v>
       </c>
       <c r="E83" s="17" t="s">
         <v>748</v>
@@ -11281,16 +11310,16 @@
         <v>67</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F84" s="17">
         <v>3</v>
@@ -11301,19 +11330,19 @@
         <v>67</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F85" s="17">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -11321,19 +11350,19 @@
         <v>67</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F86" s="17">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -11341,16 +11370,16 @@
         <v>67</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F87" s="17">
         <v>3</v>
@@ -11361,13 +11390,13 @@
         <v>67</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C88" s="17" t="s">
         <v>761</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>558</v>
+        <v>523</v>
       </c>
       <c r="E88" s="17" t="s">
         <v>762</v>
@@ -11387,13 +11416,13 @@
         <v>764</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>558</v>
+        <v>523</v>
       </c>
       <c r="E89" s="17" t="s">
         <v>765</v>
       </c>
       <c r="F89" s="17">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -11407,13 +11436,13 @@
         <v>767</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="E90" s="17" t="s">
         <v>768</v>
       </c>
       <c r="F90" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -11427,13 +11456,13 @@
         <v>770</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="E91" s="17" t="s">
         <v>771</v>
       </c>
       <c r="F91" s="17">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -11447,7 +11476,7 @@
         <v>773</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>501</v>
+        <v>571</v>
       </c>
       <c r="E92" s="17" t="s">
         <v>774</v>
@@ -11467,13 +11496,13 @@
         <v>776</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="E93" s="17" t="s">
         <v>777</v>
       </c>
       <c r="F93" s="17">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -11487,13 +11516,13 @@
         <v>779</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E94" s="17" t="s">
         <v>780</v>
       </c>
       <c r="F94" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -11507,18 +11536,18 @@
         <v>782</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E95" s="17" t="s">
         <v>783</v>
       </c>
       <c r="F95" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B96" s="17" t="s">
         <v>784</v>
@@ -11527,18 +11556,18 @@
         <v>785</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E96" s="17" t="s">
         <v>786</v>
       </c>
       <c r="F96" s="17">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B97" s="17" t="s">
         <v>787</v>
@@ -11547,18 +11576,18 @@
         <v>788</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E97" s="17" t="s">
         <v>789</v>
       </c>
       <c r="F97" s="17">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B98" s="17" t="s">
         <v>790</v>
@@ -11567,18 +11596,18 @@
         <v>791</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E98" s="17" t="s">
         <v>792</v>
       </c>
       <c r="F98" s="17">
-        <v>53</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B99" s="17" t="s">
         <v>793</v>
@@ -11587,7 +11616,7 @@
         <v>794</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E99" s="17" t="s">
         <v>795</v>
@@ -11607,13 +11636,13 @@
         <v>797</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E100" s="17" t="s">
         <v>798</v>
       </c>
       <c r="F100" s="17">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -11621,19 +11650,19 @@
         <v>70</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>781</v>
+        <v>799</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D101" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E101" s="17" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F101" s="17">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -11641,19 +11670,19 @@
         <v>70</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F102" s="17">
-        <v>6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -11661,159 +11690,159 @@
         <v>70</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C103" s="17" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D103" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F103" s="17">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="17" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F104" s="17">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="17" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>810</v>
+        <v>793</v>
       </c>
       <c r="C105" s="17" t="s">
         <v>811</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E105" s="17" t="s">
         <v>812</v>
       </c>
       <c r="F105" s="17">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="17" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>594</v>
+        <v>813</v>
       </c>
       <c r="C106" s="17" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F106" s="17">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="17" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C107" s="17" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F107" s="17">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="17" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C108" s="17" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F108" s="17">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="17" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C109" s="17" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F109" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="17" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>824</v>
+        <v>606</v>
       </c>
       <c r="C110" s="17" t="s">
         <v>825</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E110" s="17" t="s">
         <v>826</v>
       </c>
       <c r="F110" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -11827,13 +11856,13 @@
         <v>828</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E111" s="17" t="s">
         <v>829</v>
       </c>
       <c r="F111" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -11847,13 +11876,13 @@
         <v>831</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E112" s="17" t="s">
         <v>832</v>
       </c>
       <c r="F112" s="17">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -11867,13 +11896,13 @@
         <v>834</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E113" s="17" t="s">
         <v>835</v>
       </c>
       <c r="F113" s="17">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -11887,13 +11916,13 @@
         <v>837</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E114" s="17" t="s">
         <v>838</v>
       </c>
       <c r="F114" s="17">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -11907,7 +11936,7 @@
         <v>840</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E115" s="17" t="s">
         <v>841</v>
@@ -11927,13 +11956,13 @@
         <v>843</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E116" s="17" t="s">
         <v>844</v>
       </c>
       <c r="F116" s="17">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -11947,13 +11976,13 @@
         <v>846</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E117" s="17" t="s">
         <v>847</v>
       </c>
       <c r="F117" s="17">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -11967,7 +11996,7 @@
         <v>849</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E118" s="17" t="s">
         <v>850</v>
@@ -11987,13 +12016,13 @@
         <v>852</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E119" s="17" t="s">
         <v>853</v>
       </c>
       <c r="F119" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -12007,13 +12036,13 @@
         <v>855</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E120" s="17" t="s">
         <v>856</v>
       </c>
       <c r="F120" s="17">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -12027,13 +12056,13 @@
         <v>858</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E121" s="17" t="s">
         <v>859</v>
       </c>
       <c r="F121" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -12047,7 +12076,7 @@
         <v>861</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E122" s="17" t="s">
         <v>862</v>
@@ -12067,13 +12096,13 @@
         <v>864</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E123" s="17" t="s">
         <v>865</v>
       </c>
       <c r="F123" s="17">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -12087,13 +12116,13 @@
         <v>867</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E124" s="17" t="s">
         <v>868</v>
       </c>
       <c r="F124" s="17">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -12101,19 +12130,19 @@
         <v>60</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C125" s="17" t="s">
-        <v>416</v>
+        <v>870</v>
       </c>
       <c r="D125" s="17" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="F125" s="17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -12121,16 +12150,16 @@
         <v>60</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C126" s="17" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D126" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="F126" s="17">
         <v>2</v>
@@ -12138,67 +12167,67 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="17" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C127" s="17" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="F127" s="17">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="17" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C128" s="17" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E128" s="17" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="F128" s="17">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="17" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C129" s="17" t="s">
-        <v>880</v>
+        <v>415</v>
       </c>
       <c r="D129" s="17" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E129" s="17" t="s">
         <v>881</v>
       </c>
       <c r="F129" s="17">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="17" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B130" s="17" t="s">
         <v>882</v>
@@ -12207,13 +12236,13 @@
         <v>883</v>
       </c>
       <c r="D130" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E130" s="17" t="s">
         <v>884</v>
       </c>
       <c r="F130" s="17">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -12227,7 +12256,7 @@
         <v>886</v>
       </c>
       <c r="D131" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E131" s="17" t="s">
         <v>887</v>
@@ -12247,18 +12276,18 @@
         <v>889</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E132" s="17" t="s">
         <v>890</v>
       </c>
       <c r="F132" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="17" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B133" s="17" t="s">
         <v>891</v>
@@ -12267,18 +12296,18 @@
         <v>892</v>
       </c>
       <c r="D133" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E133" s="17" t="s">
         <v>893</v>
       </c>
       <c r="F133" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="17" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B134" s="17" t="s">
         <v>894</v>
@@ -12287,18 +12316,18 @@
         <v>895</v>
       </c>
       <c r="D134" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E134" s="17" t="s">
         <v>896</v>
       </c>
       <c r="F134" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="17" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B135" s="17" t="s">
         <v>897</v>
@@ -12307,18 +12336,18 @@
         <v>898</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E135" s="17" t="s">
         <v>899</v>
       </c>
       <c r="F135" s="17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="17" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B136" s="17" t="s">
         <v>900</v>
@@ -12327,13 +12356,13 @@
         <v>901</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E136" s="17" t="s">
         <v>902</v>
       </c>
       <c r="F136" s="17">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -12347,13 +12376,13 @@
         <v>904</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E137" s="17" t="s">
         <v>905</v>
       </c>
       <c r="F137" s="17">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -12367,13 +12396,13 @@
         <v>907</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E138" s="17" t="s">
         <v>908</v>
       </c>
       <c r="F138" s="17">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -12381,19 +12410,19 @@
         <v>52</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>699</v>
+        <v>909</v>
       </c>
       <c r="C139" s="17" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E139" s="17" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F139" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -12401,19 +12430,19 @@
         <v>52</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>709</v>
+        <v>912</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E140" s="17" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="F140" s="17">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -12421,19 +12450,19 @@
         <v>52</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E141" s="17" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="F141" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -12441,19 +12470,19 @@
         <v>52</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E142" s="17" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="F142" s="17">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -12461,19 +12490,19 @@
         <v>52</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>919</v>
+        <v>711</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E143" s="17" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="F143" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -12481,19 +12510,19 @@
         <v>52</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>922</v>
+        <v>721</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>405</v>
+        <v>923</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>548</v>
+        <v>523</v>
       </c>
       <c r="E144" s="17" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F144" s="17">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -12501,19 +12530,19 @@
         <v>52</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E145" s="17" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F145" s="17">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -12521,299 +12550,299 @@
         <v>52</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>740</v>
+        <v>928</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>408</v>
+        <v>929</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="E146" s="17" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="F146" s="17">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="17" t="s">
-        <v>398</v>
+        <v>52</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>737</v>
+        <v>931</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>400</v>
+        <v>932</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="E147" s="17" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="F147" s="17">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="17" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="C148" s="17" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>930</v>
+        <v>561</v>
       </c>
       <c r="E148" s="17" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="F148" s="17">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="17" t="s">
-        <v>197</v>
+        <v>52</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="C149" s="17" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>930</v>
+        <v>523</v>
       </c>
       <c r="E149" s="17" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="F149" s="17">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="17" t="s">
-        <v>197</v>
+        <v>52</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>603</v>
+        <v>752</v>
       </c>
       <c r="C150" s="17" t="s">
-        <v>935</v>
+        <v>407</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>930</v>
+        <v>501</v>
       </c>
       <c r="E150" s="17" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F150" s="17">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="17" t="s">
-        <v>197</v>
+        <v>397</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>937</v>
+        <v>749</v>
       </c>
       <c r="C151" s="17" t="s">
-        <v>938</v>
+        <v>399</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>930</v>
+        <v>505</v>
       </c>
       <c r="E151" s="17" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F151" s="17">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="17" t="s">
-        <v>197</v>
+        <v>41</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C152" s="17" t="s">
-        <v>941</v>
+        <v>396</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E152" s="17" t="s">
-        <v>927</v>
+        <v>943</v>
       </c>
       <c r="F152" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="17" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>672</v>
+        <v>944</v>
       </c>
       <c r="C153" s="17" t="s">
+        <v>945</v>
+      </c>
+      <c r="D153" s="17" t="s">
         <v>942</v>
       </c>
-      <c r="D153" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="E153" s="17" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="F153" s="17">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="17" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>944</v>
+        <v>615</v>
       </c>
       <c r="C154" s="17" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E154" s="17" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="F154" s="17">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="17" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C155" s="17" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E155" s="17" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="F155" s="17">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="17" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>919</v>
+        <v>952</v>
       </c>
       <c r="C156" s="17" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="D156" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E156" s="17" t="s">
-        <v>951</v>
+        <v>939</v>
       </c>
       <c r="F156" s="17">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="17" t="s">
-        <v>38</v>
+        <v>194</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>952</v>
+        <v>684</v>
       </c>
       <c r="C157" s="17" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E157" s="17" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F157" s="17">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="17" t="s">
-        <v>38</v>
+        <v>194</v>
       </c>
       <c r="B158" s="17" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C158" s="17" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E158" s="17" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F158" s="17">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="17" t="s">
-        <v>38</v>
+        <v>194</v>
       </c>
       <c r="B159" s="17" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C159" s="17" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D159" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E159" s="17" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F159" s="17">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="17" t="s">
-        <v>38</v>
+        <v>194</v>
       </c>
       <c r="B160" s="17" t="s">
-        <v>961</v>
+        <v>931</v>
       </c>
       <c r="C160" s="17" t="s">
         <v>962</v>
       </c>
       <c r="D160" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E160" s="17" t="s">
         <v>963</v>
       </c>
       <c r="F160" s="17">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -12821,19 +12850,19 @@
         <v>38</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>563</v>
+        <v>964</v>
       </c>
       <c r="C161" s="17" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D161" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E161" s="17" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F161" s="17">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -12841,19 +12870,19 @@
         <v>38</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C162" s="17" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D162" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E162" s="17" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F162" s="17">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -12861,19 +12890,19 @@
         <v>38</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C163" s="17" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D163" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E163" s="17" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F163" s="17">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -12881,19 +12910,19 @@
         <v>38</v>
       </c>
       <c r="B164" s="17" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C164" s="17" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D164" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E164" s="17" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F164" s="17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -12901,19 +12930,19 @@
         <v>38</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>975</v>
+        <v>576</v>
       </c>
       <c r="C165" s="17" t="s">
         <v>976</v>
       </c>
       <c r="D165" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E165" s="17" t="s">
         <v>977</v>
       </c>
       <c r="F165" s="17">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -12921,19 +12950,19 @@
         <v>38</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>842</v>
+        <v>978</v>
       </c>
       <c r="C166" s="17" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D166" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E166" s="17" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F166" s="17">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -12941,19 +12970,19 @@
         <v>38</v>
       </c>
       <c r="B167" s="17" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C167" s="17" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D167" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E167" s="17" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F167" s="17">
-        <v>80</v>
+        <v>39</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -12961,19 +12990,19 @@
         <v>38</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C168" s="17" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D168" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E168" s="17" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F168" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -12981,19 +13010,19 @@
         <v>38</v>
       </c>
       <c r="B169" s="17" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C169" s="17" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D169" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E169" s="17" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F169" s="17">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -13001,19 +13030,19 @@
         <v>38</v>
       </c>
       <c r="B170" s="17" t="s">
-        <v>989</v>
+        <v>854</v>
       </c>
       <c r="C170" s="17" t="s">
         <v>990</v>
       </c>
       <c r="D170" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E170" s="17" t="s">
         <v>991</v>
       </c>
       <c r="F170" s="17">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -13027,13 +13056,13 @@
         <v>993</v>
       </c>
       <c r="D171" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E171" s="17" t="s">
         <v>994</v>
       </c>
       <c r="F171" s="17">
-        <v>37</v>
+        <v>80</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -13047,13 +13076,13 @@
         <v>996</v>
       </c>
       <c r="D172" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E172" s="17" t="s">
         <v>997</v>
       </c>
       <c r="F172" s="17">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -13061,19 +13090,19 @@
         <v>38</v>
       </c>
       <c r="B173" s="17" t="s">
-        <v>696</v>
+        <v>998</v>
       </c>
       <c r="C173" s="17" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D173" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E173" s="17" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F173" s="17">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -13081,19 +13110,19 @@
         <v>38</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>725</v>
+        <v>1001</v>
       </c>
       <c r="C174" s="17" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D174" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E174" s="17" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="F174" s="17">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -13101,19 +13130,19 @@
         <v>38</v>
       </c>
       <c r="B175" s="17" t="s">
-        <v>919</v>
+        <v>1004</v>
       </c>
       <c r="C175" s="17" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="D175" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E175" s="17" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="F175" s="17">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -13121,63 +13150,143 @@
         <v>38</v>
       </c>
       <c r="B176" s="17" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C176" s="17" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="D176" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E176" s="17" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="F176" s="17">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="17" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B177" s="17" t="s">
-        <v>1007</v>
+        <v>708</v>
       </c>
       <c r="C177" s="17" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="D177" s="17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="E177" s="17" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="F177" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B178" s="17" t="s">
+        <v>737</v>
+      </c>
+      <c r="C178" s="17" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D178" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="E178" s="17" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F178" s="17">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B179" s="17" t="s">
+        <v>931</v>
+      </c>
+      <c r="C179" s="17" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D179" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="E179" s="17" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F179" s="17">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B180" s="17" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C180" s="17" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D180" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="E180" s="17" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F180" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B178" s="17" t="s">
-        <v>743</v>
-      </c>
-      <c r="C178" s="17" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D178" s="17" t="s">
-        <v>930</v>
-      </c>
-      <c r="E178" s="17" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F178" s="17">
+      <c r="B181" s="17" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C181" s="17" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D181" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="E181" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F181" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B182" s="17" t="s">
+        <v>755</v>
+      </c>
+      <c r="C182" s="17" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D182" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="E182" s="17" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F182" s="17">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F178"/>
+  <autoFilter ref="A1:F182"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13193,55 +13302,55 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1012</v>
+        <v>1024</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1015</v>
+        <v>1027</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1016</v>
+        <v>1028</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>1022</v>
+        <v>1034</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>1023</v>
+        <v>1035</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>1024</v>
+        <v>1036</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>1025</v>
+        <v>1037</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>1027</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -13252,7 +13361,7 @@
         <v>37</v>
       </c>
       <c r="C2" s="17">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="17">
         <v>3</v>
@@ -13261,10 +13370,10 @@
         <v>5</v>
       </c>
       <c r="F2" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="17">
-        <v>73</v>
+        <v>75.7</v>
       </c>
       <c r="H2" s="17">
         <v>22</v>
@@ -13273,19 +13382,19 @@
         <v>15</v>
       </c>
       <c r="J2" s="17">
-        <v>24.03</v>
+        <v>24.53</v>
       </c>
       <c r="K2" s="17">
         <v>84.70999999999999</v>
       </c>
       <c r="L2" s="17">
-        <v>28.4</v>
+        <v>29</v>
       </c>
       <c r="M2" s="17">
-        <v>60.67</v>
+        <v>60.17</v>
       </c>
       <c r="N2" s="17">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="O2" s="17">
         <v>52.17</v>
@@ -13299,7 +13408,7 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B3" s="17">
         <v>15</v>
@@ -13352,7 +13461,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B4" s="17">
         <v>23</v>
@@ -13405,7 +13514,7 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B5" s="17">
         <v>5</v>
@@ -13458,13 +13567,13 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B6" s="17">
         <v>6</v>
       </c>
       <c r="C6" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="17">
         <v>1</v>
@@ -13473,10 +13582,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="17">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="H6" s="17">
         <v>5</v>
@@ -13506,18 +13615,18 @@
         <v>0</v>
       </c>
       <c r="Q6" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="17" t="s">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="B7" s="17">
         <v>86</v>
       </c>
       <c r="C7" s="17">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D7" s="17">
         <v>5</v>
@@ -13526,10 +13635,10 @@
         <v>13</v>
       </c>
       <c r="F7" s="17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G7" s="17">
-        <v>68.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H7" s="17">
         <v>62</v>
@@ -13538,19 +13647,19 @@
         <v>24</v>
       </c>
       <c r="J7" s="17">
-        <v>78.18000000000001</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="K7" s="17">
         <v>249.89</v>
       </c>
       <c r="L7" s="17">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="M7" s="17">
-        <v>171.7</v>
+        <v>171.2</v>
       </c>
       <c r="N7" s="17">
-        <v>119.53</v>
+        <v>119.03</v>
       </c>
       <c r="O7" s="17">
         <v>52.17</v>
@@ -13559,12 +13668,12 @@
         <v>0</v>
       </c>
       <c r="Q7" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -13581,7 +13690,7 @@
     </row>
     <row r="10" spans="1:17" ht="30" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>1030</v>
+        <v>1042</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -13598,7 +13707,7 @@
     </row>
     <row r="11" spans="1:17" ht="30" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>1031</v>
+        <v>1043</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -13615,7 +13724,7 @@
     </row>
     <row r="12" spans="1:17" ht="30" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>1032</v>
+        <v>1044</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -13632,7 +13741,7 @@
     </row>
     <row r="13" spans="1:17" ht="30" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>1033</v>
+        <v>1045</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -13662,7 +13771,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -13681,7 +13790,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
-        <v>1034</v>
+        <v>1046</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>10</v>
@@ -13690,7 +13799,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>13</v>
@@ -13699,10 +13808,10 @@
         <v>14</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1036</v>
+        <v>1048</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>17</v>
@@ -13711,24 +13820,24 @@
         <v>12</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>1037</v>
+        <v>1049</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>1038</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>320</v>
-      </c>
       <c r="D2" s="17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E2" s="17" t="s">
         <v>31</v>
@@ -13737,7 +13846,7 @@
         <v>67</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>1039</v>
+        <v>1051</v>
       </c>
       <c r="H2" s="17">
         <v>2</v>
@@ -13747,30 +13856,30 @@
         <v>4</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="L2" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B3" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="D3" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>356</v>
-      </c>
       <c r="F3" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
@@ -13779,33 +13888,33 @@
         <v>5</v>
       </c>
       <c r="K3" s="17" t="s">
-        <v>1042</v>
+        <v>1054</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>1043</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="17" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B4" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="D4" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="E4" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="D4" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>281</v>
-      </c>
       <c r="F4" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>1044</v>
+        <v>1056</v>
       </c>
       <c r="H4" s="17">
         <v>8</v>
@@ -13815,27 +13924,27 @@
         <v>5</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B5" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>218</v>
-      </c>
       <c r="D5" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>67</v>
@@ -13843,88 +13952,88 @@
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
       <c r="I5" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J5" s="17" t="s">
         <v>4</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>1045</v>
+        <v>1057</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B6" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="C6" s="17" t="s">
-        <v>349</v>
-      </c>
       <c r="D6" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="17"/>
       <c r="I6" s="17" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J6" s="17" t="s">
         <v>5</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>1043</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B7" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>305</v>
-      </c>
       <c r="D7" s="17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>31</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>1046</v>
+        <v>1058</v>
       </c>
       <c r="H7" s="17">
         <v>3.5</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J7" s="17" t="s">
         <v>6</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>1045</v>
+        <v>1057</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -13935,7 +14044,7 @@
         <v>137</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>42</v>
@@ -13947,7 +14056,7 @@
         <v>70</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>1047</v>
+        <v>1059</v>
       </c>
       <c r="H8" s="17">
         <v>7</v>
@@ -13957,10 +14066,10 @@
         <v>4</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>1048</v>
+        <v>1060</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -13983,7 +14092,7 @@
         <v>70</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
       <c r="H9" s="17">
         <v>11</v>
@@ -13995,10 +14104,10 @@
         <v>5</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -14006,22 +14115,22 @@
         <v>135</v>
       </c>
       <c r="B10" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="C10" s="17" t="s">
-        <v>284</v>
-      </c>
       <c r="D10" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>1050</v>
+        <v>1062</v>
       </c>
       <c r="H10" s="17">
         <v>16</v>
@@ -14031,10 +14140,10 @@
         <v>5</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="L10" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -14042,10 +14151,10 @@
         <v>135</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>42</v>
@@ -14054,10 +14163,10 @@
         <v>31</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>1051</v>
+        <v>1063</v>
       </c>
       <c r="H11" s="17">
         <v>7</v>
@@ -14069,33 +14178,33 @@
         <v>5</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B12" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="17" t="s">
-        <v>286</v>
-      </c>
       <c r="D12" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>1053</v>
+        <v>1065</v>
       </c>
       <c r="H12" s="17">
         <v>16</v>
@@ -14105,33 +14214,33 @@
         <v>5</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B13" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="C13" s="17" t="s">
-        <v>289</v>
-      </c>
       <c r="D13" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>1054</v>
+        <v>1066</v>
       </c>
       <c r="H13" s="17">
         <v>24</v>
@@ -14141,33 +14250,33 @@
         <v>5</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="L13" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B14" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>292</v>
-      </c>
       <c r="D14" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>1055</v>
+        <v>1067</v>
       </c>
       <c r="H14" s="17">
         <v>16</v>
@@ -14177,10 +14286,10 @@
         <v>5</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="L14" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -14203,7 +14312,7 @@
         <v>77</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
       <c r="H15" s="17">
         <v>2.5</v>
@@ -14215,10 +14324,10 @@
         <v>4</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -14226,13 +14335,13 @@
         <v>126</v>
       </c>
       <c r="B16" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>309</v>
-      </c>
       <c r="D16" s="17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>31</v>
@@ -14241,22 +14350,22 @@
         <v>77</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="H16" s="17">
         <v>6</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J16" s="17" t="s">
         <v>6</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>1059</v>
+        <v>1071</v>
       </c>
       <c r="L16" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -14264,10 +14373,10 @@
         <v>126</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>42</v>
@@ -14279,22 +14388,22 @@
         <v>119</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="H17" s="17">
         <v>17.38</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>4</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
       <c r="L17" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -14302,10 +14411,10 @@
         <v>126</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>42</v>
@@ -14317,22 +14426,22 @@
         <v>119</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>1061</v>
+        <v>1073</v>
       </c>
       <c r="H18" s="17">
         <v>2.75</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>5</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
       <c r="L18" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -14340,10 +14449,10 @@
         <v>126</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>42</v>
@@ -14352,23 +14461,23 @@
         <v>31</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G19" s="17"/>
       <c r="H19" s="17">
         <v>4.55</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J19" s="17" t="s">
         <v>6</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
       <c r="L19" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -14376,10 +14485,10 @@
         <v>126</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>42</v>
@@ -14388,48 +14497,48 @@
         <v>31</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
       <c r="H20" s="17">
         <v>8</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>5</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>1063</v>
+        <v>1075</v>
       </c>
       <c r="L20" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B21" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>295</v>
-      </c>
       <c r="D21" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>1064</v>
+        <v>1076</v>
       </c>
       <c r="H21" s="17">
         <v>16</v>
@@ -14439,55 +14548,55 @@
         <v>5</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="L21" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B22" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="C22" s="17" t="s">
-        <v>352</v>
-      </c>
       <c r="D22" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>5</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L22" s="17" t="s">
-        <v>1043</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>42</v>
@@ -14496,7 +14605,7 @@
         <v>31</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
@@ -14507,30 +14616,30 @@
         <v>5</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
       <c r="L23" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B24" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="C24" s="17" t="s">
-        <v>366</v>
-      </c>
       <c r="D24" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>31</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
@@ -14539,30 +14648,30 @@
         <v>5</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="L24" s="17" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B25" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="D25" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="F25" s="17" t="s">
         <v>369</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>345</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>370</v>
       </c>
       <c r="G25" s="17"/>
       <c r="H25" s="17"/>
@@ -14571,30 +14680,30 @@
         <v>5</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="L25" s="17" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="17" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B26" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="C26" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="C26" s="17" t="s">
-        <v>373</v>
-      </c>
       <c r="D26" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>31</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
@@ -14603,308 +14712,236 @@
         <v>5</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="L26" s="17" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="B27" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" s="17" t="s">
         <v>194</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>197</v>
       </c>
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
       <c r="I27" s="17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J27" s="17" t="s">
         <v>6</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="L27" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>327</v>
+        <v>201</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>328</v>
+        <v>202</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>314</v>
+        <v>189</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>31</v>
+        <v>193</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
+        <v>77</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H28" s="17">
+        <v>0.25</v>
+      </c>
       <c r="I28" s="17" t="s">
-        <v>318</v>
+        <v>204</v>
       </c>
       <c r="J28" s="17" t="s">
         <v>6</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="L28" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>202</v>
+        <v>328</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>203</v>
+        <v>329</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>192</v>
+        <v>313</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>1068</v>
+        <v>1081</v>
       </c>
       <c r="H29" s="17">
-        <v>0.25</v>
-      </c>
-      <c r="I29" s="17" t="s">
-        <v>205</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="I29" s="17"/>
       <c r="J29" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K29" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="L29" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>31</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>1069</v>
+        <v>1082</v>
       </c>
       <c r="H30" s="17">
-        <v>0.03</v>
-      </c>
-      <c r="I30" s="17"/>
+        <v>2</v>
+      </c>
+      <c r="I30" s="17" t="s">
+        <v>303</v>
+      </c>
       <c r="J30" s="17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="L30" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>31</v>
+        <v>193</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="H31" s="17">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K31" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="L31" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>312</v>
+        <v>205</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>313</v>
+        <v>206</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>297</v>
+        <v>189</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>31</v>
+        <v>193</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>46</v>
+        <v>195</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>1071</v>
+        <v>1083</v>
       </c>
       <c r="H32" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="17" t="s">
-        <v>304</v>
+        <v>207</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>6</v>
       </c>
       <c r="K32" s="17" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="L32" s="17" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>1068</v>
-      </c>
-      <c r="H33" s="17">
-        <v>0.25</v>
-      </c>
-      <c r="I33" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="J33" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="L33" s="17" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>1072</v>
-      </c>
-      <c r="H34" s="17">
-        <v>1</v>
-      </c>
-      <c r="I34" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="J34" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="K34" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="L34" s="17" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L34"/>
+  <autoFilter ref="A1:L32"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>